--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_O_CHAMAL-CSTD-0-00-C-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_O_CHAMAL-CSTD-0-00-C-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\10_mcu\19epfv3_mcu_app_mainline\src\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55656ED-10CB-4CEF-8FC1-7125043807BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C4C978-E57A-4E30-87BE-E765C99F5B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7575" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14535" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="13" r:id="rId1"/>
@@ -674,7 +674,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2965" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="352">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -3362,19 +3362,12 @@
     <t>O_CHAMAL-CSTD-0-MEF01-REQ03</t>
   </si>
   <si>
-    <t>LW</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ENG1G92_STS</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ENG1G92_STS</t>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>○</t>
   </si>
   <si>
     <t>点灯(充電警告灯：赤)</t>
@@ -3596,9 +3589,6 @@
     <t>1.0.1</t>
   </si>
   <si>
-    <t>(株)NTTデータMSE</t>
-  </si>
-  <si>
     <t>承認</t>
     <rPh sb="0" eb="2">
       <t>ショウニン</t>
@@ -3717,6 +3707,43 @@
     <t>品質総点検(R4)：Alert設計書の修正対応
 [O_CHAMAL]シート
 ・数式の変更</t>
+  </si>
+  <si>
+    <t>(株)デンソー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1.0.2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DTPH Kiko</t>
+  </si>
+  <si>
+    <t>－</t>
+  </si>
+  <si>
+    <t>BEVシス検ADAS
+課題対応（BEV3CDCMET-2941）
+[Matrix]シート
+・RWの記載を変更（○→ー）
+[CH_Design]シート
+・RWの記載を変更（LW→ー）
+[O_CHAMAL]シート
+・AU8の数式を修正（NULL→vdp_PTR_NA）</t>
+    <rPh sb="11" eb="13">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>スウシキ</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -4060,7 +4087,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="79">
+  <borders count="81">
     <border>
       <left/>
       <right/>
@@ -5076,6 +5103,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -5088,7 +5141,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="296">
+  <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5785,6 +5838,21 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5794,6 +5862,9 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5818,9 +5889,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6259,61 +6327,44 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>89647</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>123265</xdr:rowOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>89647</xdr:colOff>
+      <xdr:colOff>134399</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>52108</xdr:rowOff>
+      <xdr:rowOff>103957</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
+        <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17ADB636-AFF0-E1D8-649D-F4DF3200F06F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A9EC24D-7731-63BB-245E-3D5ABD7ADFE0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="5042647" y="8124265"/>
-          <a:ext cx="582706" cy="556372"/>
+          <a:off x="5098676" y="8157882"/>
+          <a:ext cx="571429" cy="571429"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -11219,17 +11270,17 @@
       <sheetName val="４．ナビモデル"/>
       <sheetName val="３．サウンドモデル"/>
       <sheetName val="２．ラジオモデル"/>
+      <sheetName val="1.概述"/>
       <sheetName val="V200複合試験_担当分け_(2)1"/>
       <sheetName val="Spec_List_(19MC-DCM)_1"/>
       <sheetName val="Cooling_Unit"/>
-      <sheetName val="1.概述"/>
       <sheetName val="OpenIssueList"/>
-      <sheetName val="PullDown"/>
       <sheetName val="ECU基盤"/>
       <sheetName val="Name2"/>
       <sheetName val="Name3"/>
       <sheetName val="Company"/>
       <sheetName val="Name"/>
+      <sheetName val="PullDown"/>
       <sheetName val="エンジン型式"/>
       <sheetName val="分类数据"/>
       <sheetName val="index"/>
@@ -11261,6 +11312,42 @@
       <sheetName val="改訂履歴"/>
       <sheetName val="Sheet1"/>
       <sheetName val="⑥フューエル"/>
+      <sheetName val="STEP1-Definition"/>
+      <sheetName val="No.31"/>
+      <sheetName val="階層一覧"/>
+      <sheetName val="测试计划"/>
+      <sheetName val="2.2.4_起動終了時"/>
+      <sheetName val="全戻りﾊﾞｸﾞ"/>
+      <sheetName val="DataShare"/>
+      <sheetName val="ＯＰＭ設備"/>
+      <sheetName val="償却計算"/>
+      <sheetName val="技術費"/>
+      <sheetName val="消耗材"/>
+      <sheetName val="生産用消耗工具費"/>
+      <sheetName val="投資込みＭＪ原価"/>
+      <sheetName val="ＭＪ加工費"/>
+      <sheetName val="仕損根拠"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="ERRＩＤ90"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="調査シート"/>
+      <sheetName val="SCH"/>
+      <sheetName val="发行控制"/>
+      <sheetName val="Vibrate test"/>
+      <sheetName val="Data"/>
+      <sheetName val="注釈"/>
+      <sheetName val="仕向け決定用情報取得(GM250)"/>
+      <sheetName val="付録①（GM用）"/>
+      <sheetName val="Data.Share"/>
+      <sheetName val="Func.Share"/>
+      <sheetName val="引言"/>
+      <sheetName val="100万未満"/>
+      <sheetName val="MessageList"/>
+      <sheetName val="生産日報"/>
+      <sheetName val="dial　check"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -11341,10 +11428,10 @@
       <sheetData sheetId="57" refreshError="1"/>
       <sheetData sheetId="58" refreshError="1"/>
       <sheetData sheetId="59" refreshError="1"/>
-      <sheetData sheetId="60"/>
+      <sheetData sheetId="60" refreshError="1"/>
       <sheetData sheetId="61"/>
       <sheetData sheetId="62"/>
-      <sheetData sheetId="63" refreshError="1"/>
+      <sheetData sheetId="63"/>
       <sheetData sheetId="64" refreshError="1"/>
       <sheetData sheetId="65" refreshError="1"/>
       <sheetData sheetId="66" refreshError="1"/>
@@ -11383,6 +11470,42 @@
       <sheetData sheetId="99" refreshError="1"/>
       <sheetData sheetId="100" refreshError="1"/>
       <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
+      <sheetData sheetId="133" refreshError="1"/>
+      <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -11521,12 +11644,56 @@
       <sheetName val="Config - dspmgr"/>
       <sheetName val="凡例・注記記載用"/>
       <sheetName val="入力パラメータ"/>
-      <sheetName val="原紙"/>
       <sheetName val="マスタテーブル登録データ"/>
       <sheetName val="記入シート"/>
+      <sheetName val="原紙"/>
       <sheetName val="format"/>
       <sheetName val="検査シート"/>
       <sheetName val="1.概述"/>
+      <sheetName val="InterFace"/>
+      <sheetName val="集計表"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="日程"/>
+      <sheetName val="進捗"/>
+      <sheetName val="印刷"/>
+      <sheetName val="★ONS_MSG_list"/>
+      <sheetName val="Defined Layout Screen_Ver.0.6"/>
+      <sheetName val="ｲﾝﾊﾟｸﾄ影響台数集計表"/>
+      <sheetName val="実勢(売上)台数表"/>
+      <sheetName val="月別企画台数表"/>
+      <sheetName val="プロジェクト一覧表(現行)"/>
+      <sheetName val="限界利益表(半期別)"/>
+      <sheetName val="機種マスタ"/>
+      <sheetName val="機種ﾏｽﾀ（他車）"/>
+      <sheetName val="売上高表(半期別)"/>
+      <sheetName val="地点情報データ応答"/>
+      <sheetName val="階層一覧"/>
+      <sheetName val="リソーセス算出"/>
+      <sheetName val="定義"/>
+      <sheetName val="ドメイン一覧"/>
+      <sheetName val="変更区分一覧"/>
+      <sheetName val="難易度量一覧"/>
+      <sheetName val="ユーザ一覧"/>
+      <sheetName val="Normal(Mark)"/>
+      <sheetName val="リストデータ"/>
+      <sheetName val="②P071中計　工数パターン1312更新"/>
+      <sheetName val="FBtbl"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="入力規則"/>
+      <sheetName val="#REF"/>
+      <sheetName val="Contents"/>
+      <sheetName val="選択肢"/>
+      <sheetName val="DTF"/>
+      <sheetName val="module"/>
+      <sheetName val="DataTable"/>
+      <sheetName val="Func.Share"/>
+      <sheetName val="場所指定地図"/>
+      <sheetName val="ﾕｰｻﾞｰ設定"/>
+      <sheetName val="入力"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -11670,6 +11837,50 @@
       <sheetData sheetId="132" refreshError="1"/>
       <sheetData sheetId="133" refreshError="1"/>
       <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
+      <sheetData sheetId="141" refreshError="1"/>
+      <sheetData sheetId="142" refreshError="1"/>
+      <sheetData sheetId="143" refreshError="1"/>
+      <sheetData sheetId="144" refreshError="1"/>
+      <sheetData sheetId="145" refreshError="1"/>
+      <sheetData sheetId="146" refreshError="1"/>
+      <sheetData sheetId="147" refreshError="1"/>
+      <sheetData sheetId="148" refreshError="1"/>
+      <sheetData sheetId="149" refreshError="1"/>
+      <sheetData sheetId="150" refreshError="1"/>
+      <sheetData sheetId="151" refreshError="1"/>
+      <sheetData sheetId="152" refreshError="1"/>
+      <sheetData sheetId="153" refreshError="1"/>
+      <sheetData sheetId="154" refreshError="1"/>
+      <sheetData sheetId="155" refreshError="1"/>
+      <sheetData sheetId="156" refreshError="1"/>
+      <sheetData sheetId="157" refreshError="1"/>
+      <sheetData sheetId="158" refreshError="1"/>
+      <sheetData sheetId="159" refreshError="1"/>
+      <sheetData sheetId="160" refreshError="1"/>
+      <sheetData sheetId="161" refreshError="1"/>
+      <sheetData sheetId="162" refreshError="1"/>
+      <sheetData sheetId="163" refreshError="1"/>
+      <sheetData sheetId="164" refreshError="1"/>
+      <sheetData sheetId="165" refreshError="1"/>
+      <sheetData sheetId="166" refreshError="1"/>
+      <sheetData sheetId="167" refreshError="1"/>
+      <sheetData sheetId="168" refreshError="1"/>
+      <sheetData sheetId="169" refreshError="1"/>
+      <sheetData sheetId="170" refreshError="1"/>
+      <sheetData sheetId="171" refreshError="1"/>
+      <sheetData sheetId="172" refreshError="1"/>
+      <sheetData sheetId="173" refreshError="1"/>
+      <sheetData sheetId="174" refreshError="1"/>
+      <sheetData sheetId="175" refreshError="1"/>
+      <sheetData sheetId="176" refreshError="1"/>
+      <sheetData sheetId="177" refreshError="1"/>
+      <sheetData sheetId="178" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -11851,10 +12062,10 @@
       <sheetName val="CPF"/>
       <sheetName val="編集"/>
       <sheetName val="PAIData"/>
+      <sheetName val="⑪1ﾊﾞﾘｴｰｼｮﾝ(16LX)△１"/>
       <sheetName val="NCastalone"/>
       <sheetName val="dongia (2)"/>
       <sheetName val="Volumes"/>
-      <sheetName val="⑪1ﾊﾞﾘｴｰｼｮﾝ(16LX)△１"/>
       <sheetName val="加工費"/>
       <sheetName val="車両仕様 嗼1嗼1噌1鲌"/>
       <sheetName val="車両仕様 勜+勜+匬+鲌"/>
@@ -11864,8 +12075,8 @@
       <sheetName val="Y230"/>
       <sheetName val="MASTER"/>
       <sheetName val="設定"/>
+      <sheetName val="電子ﾎﾞﾘｭｰﾑ設定値（740Nと同一）"/>
       <sheetName val="⑥フューエル"/>
-      <sheetName val="電子ﾎﾞﾘｭｰﾑ設定値（740Nと同一）"/>
       <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ"/>
       <sheetName val="設品表01-3-23作成"/>
       <sheetName val="wire"/>
@@ -11881,25 +12092,24 @@
       <sheetName val="610L611L品番一覧"/>
       <sheetName val="【Input】見積基礎情報（海外生産分)"/>
       <sheetName val="IM-P-L-JB "/>
-      <sheetName val="797T輸入部品リスト"/>
-      <sheetName val="テーブル"/>
-      <sheetName val="Master Updated(517)"/>
-      <sheetName val="４-２．151項目累積（日本）"/>
-      <sheetName val="５-２．151項目累積（北米）"/>
-      <sheetName val="５-１．151項目詳細（北米）"/>
-      <sheetName val="545N仕様ﾗﾌ2"/>
-      <sheetName val="商品力向上"/>
-      <sheetName val="OP-PD"/>
-      <sheetName val="６２３Ｔ"/>
+      <sheetName val="RMBSS's Triggered"/>
+      <sheetName val="_"/>
       <sheetName val="Main 2"/>
       <sheetName val="Datasheet from R. Hinds"/>
-      <sheetName val="GMT900 IPC"/>
+      <sheetName val="545N仕様ﾗﾌ2"/>
+      <sheetName val="Master Updated(517)"/>
+      <sheetName val="６２３Ｔ"/>
+      <sheetName val="商品力向上"/>
+      <sheetName val="ED AND EDOV"/>
       <sheetName val="HORAS_TRAB"/>
       <sheetName val="Resumo_Corolla"/>
       <sheetName val="GASTOS_COROLLA"/>
-      <sheetName val="CALC"/>
-      <sheetName val="ﾘｽﾄ候補"/>
-      <sheetName val="ｺｰﾄﾞ表"/>
+      <sheetName val="④要素記号一覧表"/>
+      <sheetName val="START"/>
+      <sheetName val="Blue Flag"/>
+      <sheetName val="Calc Sheet Budget"/>
+      <sheetName val="見積一覧（１案）"/>
+      <sheetName val="部品"/>
       <sheetName val="①評価項目_メーカー"/>
       <sheetName val="車両仕様_x005f_x0000_4__x005f_x0000__x005f_x0011__x00"/>
       <sheetName val="車両仕様4__x005f_x0000__x005f_x0011__x005f_x0000_"/>
@@ -11926,16 +12136,9 @@
       <sheetName val="車両仕様_4___x005f_x005f_x005f_x005f_x005f_x005f_x001"/>
       <sheetName val="車両仕様4___x005f_x005f_x005f_x005f_x005f_x005f_x0011"/>
       <sheetName val="EFFY_MAZDA"/>
-      <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ用ｺｰﾄﾞ表"/>
-      <sheetName val="_"/>
-      <sheetName val="RMBSS's Triggered"/>
-      <sheetName val="ED AND EDOV"/>
-      <sheetName val="④要素記号一覧表"/>
-      <sheetName val="START"/>
-      <sheetName val="Blue Flag"/>
-      <sheetName val="Calc Sheet Budget"/>
-      <sheetName val="見積一覧（１案）"/>
-      <sheetName val="部品"/>
+      <sheetName val="４-２．151項目累積（日本）"/>
+      <sheetName val="５-２．151項目累積（北米）"/>
+      <sheetName val="５-１．151項目詳細（北米）"/>
       <sheetName val="sebelumCR"/>
       <sheetName val="08TMME"/>
       <sheetName val="VCPT"/>
@@ -11945,6 +12148,14 @@
       <sheetName val="WIP Cal Sheet"/>
       <sheetName val="Pricing overview"/>
       <sheetName val="駆動系1"/>
+      <sheetName val="797T輸入部品リスト"/>
+      <sheetName val="テーブル"/>
+      <sheetName val="OP-PD"/>
+      <sheetName val="GMT900 IPC"/>
+      <sheetName val="CALC"/>
+      <sheetName val="ﾘｽﾄ候補"/>
+      <sheetName val="ｺｰﾄﾞ表"/>
+      <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ用ｺｰﾄﾞ表"/>
       <sheetName val="393.N"/>
       <sheetName val="CæÊ _x0015_ Op"/>
       <sheetName val="ƒƒCƒ“‰æ–Ê _x0015_ Op"/>
@@ -11964,6 +12175,10 @@
       <sheetName val="車両仕様_ᵣ逰ᵣ邀ᵣ郰ᵣ"/>
       <sheetName val="他"/>
       <sheetName val="part"/>
+      <sheetName val="415T原"/>
+      <sheetName val="PAC14"/>
+      <sheetName val="部品表"/>
+      <sheetName val="■07中期明細雛形"/>
       <sheetName val="Vectra"/>
       <sheetName val="PRADO"/>
       <sheetName val="Previous"/>
@@ -12003,10 +12218,6 @@
       <sheetName val="OTHERS x620"/>
       <sheetName val="Ref"/>
       <sheetName val="TOTAL P2"/>
-      <sheetName val="415T原"/>
-      <sheetName val="PAC14"/>
-      <sheetName val="部品表"/>
-      <sheetName val="■07中期明細雛形"/>
       <sheetName val="BUYERS"/>
       <sheetName val="Status"/>
       <sheetName val="PR"/>
@@ -12994,18 +13205,18 @@
       <sheetName val="SUM"/>
       <sheetName val="ﾄﾗｯｸ"/>
       <sheetName val="00"/>
+      <sheetName val="追加検討（調光外部出力）"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="option"/>
       <sheetName val="課題管理"/>
       <sheetName val="C-55227AB"/>
       <sheetName val="Data Definition"/>
       <sheetName val="FC_まとめる"/>
-      <sheetName val="vocabulary"/>
-      <sheetName val="Calibration"/>
-      <sheetName val="CVBS"/>
-      <sheetName val="RGB"/>
       <sheetName val="車両仕様_4___x0011__x00"/>
       <sheetName val="ドメインリスト"/>
-      <sheetName val="option"/>
-      <sheetName val="追加検討（調光外部出力）"/>
       <sheetName val="入力規則"/>
       <sheetName val="Inf"/>
       <sheetName val="#REF!"/>
@@ -13096,8 +13307,29 @@
       <sheetName val="入力LIST"/>
       <sheetName val="パラメータ一覧(AXSS.AXCS)"/>
       <sheetName val="設定値定義"/>
+      <sheetName val="リストデータ"/>
+      <sheetName val="All"/>
+      <sheetName val="58831-06360"/>
+      <sheetName val="1999.4"/>
+      <sheetName val="車両仕様 _x005f_x0000__x005f_x0000__x005f_x000a__x000"/>
+      <sheetName val="車両仕様_x005f_x0000_ῃ_x005f_x0000__x005f_x0014__x000"/>
+      <sheetName val="車両仕様_x005f_x0000__x005f_x0000__x005f_x0000__x0000"/>
+      <sheetName val="車両仕様_x005f_x0000_ῆ玐ῆꆠῨ"/>
+      <sheetName val="車両仕様4?_x005f_x0000__x005f_x0000__x005f_x0000_"/>
+      <sheetName val="SHEET  car no"/>
       <sheetName val="車両仕様????帅?"/>
       <sheetName val="Net Price Position _ Sheet 1"/>
+      <sheetName val="Packing_List2"/>
+      <sheetName val="Packing_List"/>
+      <sheetName val="Calculation_PS"/>
+      <sheetName val="Customer_behaver"/>
+      <sheetName val="Seat_Assy_Tool_Tracking"/>
+      <sheetName val="Stock_in_Trade1"/>
+      <sheetName val="Packing_List21"/>
+      <sheetName val="Packing_List1"/>
+      <sheetName val="Calculation_PS1"/>
+      <sheetName val="Customer_behaver1"/>
+      <sheetName val="Seat_Assy_Tool_Tracking1"/>
       <sheetName val="POs"/>
       <sheetName val="計算式"/>
       <sheetName val="工管合計"/>
@@ -14621,15 +14853,9 @@
       <sheetName val="5"/>
       <sheetName val="確認ｼｰﾄ(TBU)"/>
       <sheetName val="Sheet1 (2)"/>
-      <sheetName val="SHEET  car no"/>
       <sheetName val="サイクル"/>
       <sheetName val="特殊サイクル一覧"/>
       <sheetName val="カメラ"/>
-      <sheetName val="車両仕様 _x005f_x0000__x005f_x0000__x005f_x000a__x000"/>
-      <sheetName val="車両仕様_x005f_x0000_ῃ_x005f_x0000__x005f_x0014__x000"/>
-      <sheetName val="車両仕様_x005f_x0000__x005f_x0000__x005f_x0000__x0000"/>
-      <sheetName val="車両仕様_x005f_x0000_ῆ玐ῆꆠῨ"/>
-      <sheetName val="車両仕様4?_x005f_x0000__x005f_x0000__x005f_x0000_"/>
       <sheetName val="台数"/>
       <sheetName val="MET397D-25"/>
       <sheetName val="集計表"/>
@@ -14638,21 +14864,6 @@
       <sheetName val="Ｓｉ問連"/>
       <sheetName val="アップロード系(2)"/>
       <sheetName val="エンジン型式"/>
-      <sheetName val="リストデータ"/>
-      <sheetName val="All"/>
-      <sheetName val="58831-06360"/>
-      <sheetName val="1999.4"/>
-      <sheetName val="Packing_List2"/>
-      <sheetName val="Packing_List"/>
-      <sheetName val="Calculation_PS"/>
-      <sheetName val="Customer_behaver"/>
-      <sheetName val="Seat_Assy_Tool_Tracking"/>
-      <sheetName val="Stock_in_Trade1"/>
-      <sheetName val="Packing_List21"/>
-      <sheetName val="Packing_List1"/>
-      <sheetName val="Calculation_PS1"/>
-      <sheetName val="Customer_behaver1"/>
-      <sheetName val="Seat_Assy_Tool_Tracking1"/>
       <sheetName val="Index"/>
       <sheetName val="Defined Layout Screen_Ver.0.6"/>
       <sheetName val="９ｘ"/>
@@ -14664,6 +14875,188 @@
       <sheetName val="config"/>
       <sheetName val="地点情報データ応答"/>
       <sheetName val="Par"/>
+      <sheetName val="Calcul"/>
+      <sheetName val="ETC機能判定"/>
+      <sheetName val="ETCメニュー"/>
+      <sheetName val="登録情報表示"/>
+      <sheetName val="ETC設定"/>
+      <sheetName val="履歴情報表示"/>
+      <sheetName val="履歴情報詳細表示"/>
+      <sheetName val="メニュー２"/>
+      <sheetName val="割込み(Disp)"/>
+      <sheetName val="割込み(Navi)"/>
+      <sheetName val="走行強制状態変化"/>
+      <sheetName val="入力パラメータ"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="InterFace"/>
+      <sheetName val="FBtbl"/>
+      <sheetName val="リスト画面"/>
+      <sheetName val="特殊画面"/>
+      <sheetName val="入力画面"/>
+      <sheetName val="メッセージ受信開始"/>
+      <sheetName val="Mark"/>
+      <sheetName val="Contents"/>
+      <sheetName val="車両仕様4_ "/>
+      <sheetName val="改正履歴"/>
+      <sheetName val="リスト選択用"/>
+      <sheetName val="变更履历"/>
+      <sheetName val="Menu List"/>
+      <sheetName val="ドメイン一覧"/>
+      <sheetName val="検査シート"/>
+      <sheetName val="Cover"/>
+      <sheetName val="MIS REPORT "/>
+      <sheetName val="（別紙5-1）PP02簡素化"/>
+      <sheetName val="universal"/>
+      <sheetName val="Cost Casting"/>
+      <sheetName val="paint mtrl"/>
+      <sheetName val="corolla_095W_"/>
+      <sheetName val="dyna"/>
+      <sheetName val="FC"/>
+      <sheetName val="★ONS_MSG_list"/>
+      <sheetName val="ﾕｰｻﾞｰ設定"/>
+      <sheetName val="同行评审"/>
+      <sheetName val="5.心配点抽出-0"/>
+      <sheetName val="0.表紙"/>
+      <sheetName val="1._概要"/>
+      <sheetName val="4 選局"/>
+      <sheetName val="定数"/>
+      <sheetName val="Case 21_1"/>
+      <sheetName val="96期(川崎)"/>
+      <sheetName val="ORDSHP"/>
+      <sheetName val="B"/>
+      <sheetName val="Blue_Flag3"/>
+      <sheetName val="Calc_Sheet_Budget3"/>
+      <sheetName val="_PART_479W_LHD3"/>
+      <sheetName val="_PART_MYY5A3"/>
+      <sheetName val="393_N3"/>
+      <sheetName val="WIP_Cal_Sheet3"/>
+      <sheetName val="Pricing_overview3"/>
+      <sheetName val="Lookup_Table3"/>
+      <sheetName val="promo_lists_20113"/>
+      <sheetName val="車両仕様_嗼1嗼1噌1鲌3"/>
+      <sheetName val="車両仕様_勜+勜+匬+鲌3"/>
+      <sheetName val="EquipmentTrimming_Cabin_NS3"/>
+      <sheetName val="Reference_3"/>
+      <sheetName val="車両仕様__x005f_x0000__x005f_x0000_?_x005f_x0012_?瞳?3"/>
+      <sheetName val="車両仕様_???_x005f_x0012_?瞳?3"/>
+      <sheetName val="160th_NPCC_Nov'103"/>
+      <sheetName val="RMBSS's_Triggered3"/>
+      <sheetName val="車両仕様?4???_??3"/>
+      <sheetName val="車両仕様_???_?瞳?3"/>
+      <sheetName val="車両仕様???ꎨ_窉瞳㾐3"/>
+      <sheetName val="車両仕様?4??_?3"/>
+      <sheetName val="車両仕様4??_?3"/>
+      <sheetName val="車両仕様____瞳_3"/>
+      <sheetName val="車両仕様______瞳_3"/>
+      <sheetName val="車両仕様_4______3"/>
+      <sheetName val="車両仕様___ꎨ_窉瞳㾐3"/>
+      <sheetName val="車両仕様_4____3"/>
+      <sheetName val="車両仕様4____3"/>
+      <sheetName val="PRICE_LIST3"/>
+      <sheetName val="Loss_Time3"/>
+      <sheetName val="Price_range_IT3"/>
+      <sheetName val="Avensis+d_seg__in_&amp;_out_of_UK+3"/>
+      <sheetName val="#ofclose__xl3"/>
+      <sheetName val="Annexes_toutes_bases3"/>
+      <sheetName val="DON_GIA3"/>
+      <sheetName val="CHITIET_VL-NC3"/>
+      <sheetName val="TONGKE3p_3"/>
+      <sheetName val="TOTAL_P23"/>
+      <sheetName val="2_-_Summary3"/>
+      <sheetName val="IPOTESI_PIANO_STATICA3"/>
+      <sheetName val="make_up3"/>
+      <sheetName val="車両仕様_???_x005f_x005f_x005f_x0012_?瞳?3"/>
+      <sheetName val="調達担当者(06_2～)3"/>
+      <sheetName val="車両仕様__x005f_x0000__2"/>
+      <sheetName val="車両仕様_x005f_x0000__N2"/>
+      <sheetName val="車両仕様___x005f_x0012_2"/>
+      <sheetName val="車両仕様__x005f_x005f_x2"/>
+      <sheetName val="車両仕様___x005f_x005f_2"/>
+      <sheetName val="05-065_she2"/>
+      <sheetName val="idgr_-_formula2"/>
+      <sheetName val="IDGR_(3)2"/>
+      <sheetName val="IDGR_(2)2"/>
+      <sheetName val="PLIV_(3)2"/>
+      <sheetName val="PLIV_(2)2"/>
+      <sheetName val="PLIV_(template)2"/>
+      <sheetName val="inv_recon2"/>
+      <sheetName val="side_member2"/>
+      <sheetName val="TTC_(FG)2"/>
+      <sheetName val="Sheet1_(3)2"/>
+      <sheetName val="truck_allocation2"/>
+      <sheetName val="Supplier_Price_Check2"/>
+      <sheetName val="$_-_june2"/>
+      <sheetName val="Vios_Cost_Reduction_actual_pro2"/>
+      <sheetName val="RET_PALLET2"/>
+      <sheetName val="Form_A2"/>
+      <sheetName val="NG_SUMMARY2"/>
+      <sheetName val="impact_pallet_and_racks2"/>
+      <sheetName val="Daily_WSD2"/>
+      <sheetName val="ass'y_12'04-05'053"/>
+      <sheetName val="Type_I2"/>
+      <sheetName val="Schedule_PM2"/>
+      <sheetName val="training_forklift2"/>
+      <sheetName val="Budget_by_Category2"/>
+      <sheetName val="investment_tmc_v8_0_34p2"/>
+      <sheetName val="PTD_Activity2"/>
+      <sheetName val="Sample_1PP_2"/>
+      <sheetName val="Open_Ran3"/>
+      <sheetName val="Open_RAN_23"/>
+      <sheetName val="CHIA_KH2"/>
+      <sheetName val="Purch__BP2"/>
+      <sheetName val="車両仕様_____x005f_x005f_x005f_x005f_x0013"/>
+      <sheetName val="車両仕様_____x005f_x005f_x005f_x005f_x0053"/>
+      <sheetName val="ＰＲＥ_NO1"/>
+      <sheetName val="Courier_4x2"/>
+      <sheetName val="Price_Trend2"/>
+      <sheetName val="車両仕様_?_x005f_x0012_?瞳?2"/>
+      <sheetName val="YARIS_HB2"/>
+      <sheetName val="00_KS"/>
+      <sheetName val="PRADO_3Dr_fl2"/>
+      <sheetName val="01_DATA2"/>
+      <sheetName val="Quality_Update2"/>
+      <sheetName val="prior_data"/>
+      <sheetName val="Table_Master"/>
+      <sheetName val="1_概述"/>
+      <sheetName val="Drop-down_Menu_List"/>
+      <sheetName val="Open_Item_List"/>
+      <sheetName val="本修正_DIFF_"/>
+      <sheetName val="Sector_Assignment"/>
+      <sheetName val="BQ_CONVEYOR"/>
+      <sheetName val="IMV_LIST_2003"/>
+      <sheetName val="車両仕様_x005f_x0000_4__x005f_x0000__x005f_x0000___x0"/>
+      <sheetName val="車両仕様__x005f_x0000__x005f_x0000____瞳_"/>
+      <sheetName val="Part_list"/>
+      <sheetName val="INACT797"/>
+      <sheetName val="M1A"/>
+      <sheetName val="OK"/>
+      <sheetName val="??? Pilling upu_S y"/>
+      <sheetName val="ASF INVENTORY"/>
+      <sheetName val="車両仕様_4___x005f_x0013__x0013__x0013__x0013__x0013_"/>
+      <sheetName val="ጀጀ؀ԀЀࠀ᐀Ѐऀ܀̀܀ഀ܀Ԁऀ଀ࠀ_x0000_"/>
+      <sheetName val="CTable"/>
+      <sheetName val="bs is"/>
+      <sheetName val="成績"/>
+      <sheetName val="IT Checklist"/>
+      <sheetName val="ﾊﾟｲﾌﾟ"/>
+      <sheetName val="冷延鋼板"/>
+      <sheetName val="熱延鋼板"/>
+      <sheetName val="他材料費"/>
+      <sheetName val="No.31"/>
+      <sheetName val="コマンド認識, DTMF"/>
+      <sheetName val="CS2_SmcDriverインテグ項目"/>
+      <sheetName val="標準仕様DB"/>
+      <sheetName val="BEEP設定"/>
+      <sheetName val="休日"/>
+      <sheetName val="工数ｺｰﾄﾞﾘｽﾄ"/>
+      <sheetName val="5．キー入力動作説明"/>
+      <sheetName val="日程"/>
+      <sheetName val="進捗"/>
+      <sheetName val="印刷"/>
+      <sheetName val="試験項目_R3小"/>
+      <sheetName val="Config_by_Program"/>
+      <sheetName val="DIAG_cfg_setting"/>
+      <sheetName val="AUBISTConfigurator_AssistTool"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -15219,33 +15612,45 @@
       <sheetData sheetId="304" refreshError="1"/>
       <sheetData sheetId="305" refreshError="1"/>
       <sheetData sheetId="306" refreshError="1"/>
-      <sheetData sheetId="307">
+      <sheetData sheetId="307" refreshError="1"/>
+      <sheetData sheetId="308" refreshError="1"/>
+      <sheetData sheetId="309" refreshError="1"/>
+      <sheetData sheetId="310" refreshError="1"/>
+      <sheetData sheetId="311">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="308">
+      <sheetData sheetId="312">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="309">
+      <sheetData sheetId="313">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="310"/>
-      <sheetData sheetId="311"/>
-      <sheetData sheetId="312" refreshError="1"/>
-      <sheetData sheetId="313" refreshError="1"/>
-      <sheetData sheetId="314" refreshError="1"/>
-      <sheetData sheetId="315" refreshError="1"/>
+      <sheetData sheetId="314">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="315">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="316" refreshError="1"/>
       <sheetData sheetId="317" refreshError="1"/>
       <sheetData sheetId="318" refreshError="1"/>
@@ -16817,8 +17222,8 @@
       </sheetData>
       <sheetData sheetId="793">
         <row r="1">
-          <cell r="B1" t="str">
-            <v>1</v>
+          <cell r="A1" t="str">
+            <v>ﾄﾖﾀ自動車株式会社　調達本部　</v>
           </cell>
         </row>
       </sheetData>
@@ -16854,7 +17259,13 @@
       <sheetData sheetId="805" refreshError="1"/>
       <sheetData sheetId="806" refreshError="1"/>
       <sheetData sheetId="807" refreshError="1"/>
-      <sheetData sheetId="808"/>
+      <sheetData sheetId="808">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="809" refreshError="1"/>
       <sheetData sheetId="810" refreshError="1"/>
       <sheetData sheetId="811" refreshError="1"/>
@@ -17817,9 +18228,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1050">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18041,9 +18452,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1082">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18062,9 +18473,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1085">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18391,9 +18802,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1132">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18482,9 +18893,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1145">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18713,16 +19124,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1178">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1179">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18762,9 +19173,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1185">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18790,9 +19201,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1189">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18811,9 +19222,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1192">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18881,9 +19292,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1202">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18902,16 +19313,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1205">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1206">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18923,16 +19334,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1208">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1209">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18972,9 +19383,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1215">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -19000,9 +19411,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1219">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -19021,9 +19432,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1222">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -19091,9 +19502,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1232">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -19112,16 +19523,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1235">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1236">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -19133,16 +19544,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1238">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1239">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -19182,16 +19593,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1245">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1246">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -19251,16 +19662,76 @@
       <sheetData sheetId="1294"/>
       <sheetData sheetId="1295" refreshError="1"/>
       <sheetData sheetId="1296" refreshError="1"/>
-      <sheetData sheetId="1297"/>
-      <sheetData sheetId="1298"/>
-      <sheetData sheetId="1299"/>
-      <sheetData sheetId="1300"/>
-      <sheetData sheetId="1301"/>
-      <sheetData sheetId="1302"/>
-      <sheetData sheetId="1303"/>
-      <sheetData sheetId="1304"/>
-      <sheetData sheetId="1305"/>
-      <sheetData sheetId="1306"/>
+      <sheetData sheetId="1297">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1298">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1299">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1300">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1301">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1302">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1303">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1304">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1305">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1306">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1307" refreshError="1"/>
       <sheetData sheetId="1308" refreshError="1"/>
       <sheetData sheetId="1309" refreshError="1"/>
@@ -19270,13 +19741,13 @@
       <sheetData sheetId="1313" refreshError="1"/>
       <sheetData sheetId="1314" refreshError="1"/>
       <sheetData sheetId="1315" refreshError="1"/>
-      <sheetData sheetId="1316"/>
+      <sheetData sheetId="1316" refreshError="1"/>
       <sheetData sheetId="1317" refreshError="1"/>
       <sheetData sheetId="1318" refreshError="1"/>
       <sheetData sheetId="1319" refreshError="1"/>
       <sheetData sheetId="1320" refreshError="1"/>
       <sheetData sheetId="1321" refreshError="1"/>
-      <sheetData sheetId="1322" refreshError="1"/>
+      <sheetData sheetId="1322"/>
       <sheetData sheetId="1323" refreshError="1"/>
       <sheetData sheetId="1324" refreshError="1"/>
       <sheetData sheetId="1325" refreshError="1"/>
@@ -19371,39 +19842,33 @@
       <sheetData sheetId="1414" refreshError="1"/>
       <sheetData sheetId="1415" refreshError="1"/>
       <sheetData sheetId="1416" refreshError="1"/>
-      <sheetData sheetId="1417"/>
+      <sheetData sheetId="1417" refreshError="1"/>
       <sheetData sheetId="1418" refreshError="1"/>
       <sheetData sheetId="1419" refreshError="1"/>
       <sheetData sheetId="1420" refreshError="1"/>
       <sheetData sheetId="1421" refreshError="1"/>
       <sheetData sheetId="1422" refreshError="1"/>
-      <sheetData sheetId="1423"/>
-      <sheetData sheetId="1424"/>
-      <sheetData sheetId="1425"/>
-      <sheetData sheetId="1426"/>
+      <sheetData sheetId="1423" refreshError="1"/>
+      <sheetData sheetId="1424" refreshError="1"/>
+      <sheetData sheetId="1425" refreshError="1"/>
+      <sheetData sheetId="1426" refreshError="1"/>
       <sheetData sheetId="1427"/>
-      <sheetData sheetId="1428"/>
+      <sheetData sheetId="1428" refreshError="1"/>
       <sheetData sheetId="1429"/>
       <sheetData sheetId="1430"/>
       <sheetData sheetId="1431"/>
       <sheetData sheetId="1432"/>
       <sheetData sheetId="1433"/>
-      <sheetData sheetId="1434" refreshError="1"/>
-      <sheetData sheetId="1435">
-        <row r="3">
-          <cell r="C3" t="str">
-            <v>2022年</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="1434"/>
+      <sheetData sheetId="1435"/>
       <sheetData sheetId="1436"/>
       <sheetData sheetId="1437"/>
       <sheetData sheetId="1438"/>
       <sheetData sheetId="1439"/>
-      <sheetData sheetId="1440"/>
-      <sheetData sheetId="1441"/>
-      <sheetData sheetId="1442"/>
-      <sheetData sheetId="1443"/>
+      <sheetData sheetId="1440" refreshError="1"/>
+      <sheetData sheetId="1441" refreshError="1"/>
+      <sheetData sheetId="1442" refreshError="1"/>
+      <sheetData sheetId="1443" refreshError="1"/>
       <sheetData sheetId="1444"/>
       <sheetData sheetId="1445"/>
       <sheetData sheetId="1446"/>
@@ -19415,8 +19880,14 @@
       <sheetData sheetId="1452"/>
       <sheetData sheetId="1453"/>
       <sheetData sheetId="1454"/>
-      <sheetData sheetId="1455"/>
-      <sheetData sheetId="1456"/>
+      <sheetData sheetId="1455" refreshError="1"/>
+      <sheetData sheetId="1456">
+        <row r="3">
+          <cell r="C3" t="str">
+            <v>2022年</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1457"/>
       <sheetData sheetId="1458"/>
       <sheetData sheetId="1459"/>
@@ -19496,19 +19967,73 @@
       <sheetData sheetId="1533"/>
       <sheetData sheetId="1534"/>
       <sheetData sheetId="1535"/>
-      <sheetData sheetId="1536"/>
-      <sheetData sheetId="1537"/>
+      <sheetData sheetId="1536">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1537">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1538"/>
-      <sheetData sheetId="1539"/>
+      <sheetData sheetId="1539">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1540"/>
-      <sheetData sheetId="1541"/>
-      <sheetData sheetId="1542"/>
-      <sheetData sheetId="1543"/>
+      <sheetData sheetId="1541">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1542">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1543">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1544"/>
-      <sheetData sheetId="1545"/>
+      <sheetData sheetId="1545">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1546"/>
-      <sheetData sheetId="1547"/>
-      <sheetData sheetId="1548"/>
+      <sheetData sheetId="1547">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1548">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1549"/>
       <sheetData sheetId="1550"/>
       <sheetData sheetId="1551"/>
@@ -20898,52 +21423,52 @@
       <sheetData sheetId="2935"/>
       <sheetData sheetId="2936"/>
       <sheetData sheetId="2937"/>
-      <sheetData sheetId="2938">
+      <sheetData sheetId="2938"/>
+      <sheetData sheetId="2939"/>
+      <sheetData sheetId="2940"/>
+      <sheetData sheetId="2941"/>
+      <sheetData sheetId="2942"/>
+      <sheetData sheetId="2943"/>
+      <sheetData sheetId="2944"/>
+      <sheetData sheetId="2945"/>
+      <sheetData sheetId="2946"/>
+      <sheetData sheetId="2947"/>
+      <sheetData sheetId="2948"/>
+      <sheetData sheetId="2949"/>
+      <sheetData sheetId="2950"/>
+      <sheetData sheetId="2951"/>
+      <sheetData sheetId="2952"/>
+      <sheetData sheetId="2953"/>
+      <sheetData sheetId="2954"/>
+      <sheetData sheetId="2955"/>
+      <sheetData sheetId="2956"/>
+      <sheetData sheetId="2957"/>
+      <sheetData sheetId="2958"/>
+      <sheetData sheetId="2959">
         <row r="1">
           <cell r="A1"/>
         </row>
       </sheetData>
-      <sheetData sheetId="2939"/>
-      <sheetData sheetId="2940"/>
-      <sheetData sheetId="2941"/>
-      <sheetData sheetId="2942" refreshError="1"/>
-      <sheetData sheetId="2943">
+      <sheetData sheetId="2960"/>
+      <sheetData sheetId="2961"/>
+      <sheetData sheetId="2962"/>
+      <sheetData sheetId="2963">
         <row r="1">
           <cell r="B1" t="str">
             <v>文章管理番号</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2944"/>
-      <sheetData sheetId="2945" refreshError="1"/>
-      <sheetData sheetId="2946" refreshError="1"/>
-      <sheetData sheetId="2947" refreshError="1"/>
-      <sheetData sheetId="2948" refreshError="1"/>
-      <sheetData sheetId="2949" refreshError="1"/>
-      <sheetData sheetId="2950" refreshError="1"/>
-      <sheetData sheetId="2951" refreshError="1"/>
-      <sheetData sheetId="2952" refreshError="1"/>
-      <sheetData sheetId="2953" refreshError="1"/>
-      <sheetData sheetId="2954" refreshError="1"/>
-      <sheetData sheetId="2955" refreshError="1"/>
-      <sheetData sheetId="2956" refreshError="1"/>
-      <sheetData sheetId="2957" refreshError="1"/>
-      <sheetData sheetId="2958" refreshError="1"/>
-      <sheetData sheetId="2959" refreshError="1"/>
-      <sheetData sheetId="2960" refreshError="1"/>
-      <sheetData sheetId="2961" refreshError="1"/>
-      <sheetData sheetId="2962" refreshError="1"/>
-      <sheetData sheetId="2963"/>
       <sheetData sheetId="2964"/>
-      <sheetData sheetId="2965"/>
-      <sheetData sheetId="2966"/>
-      <sheetData sheetId="2967"/>
-      <sheetData sheetId="2968"/>
-      <sheetData sheetId="2969"/>
-      <sheetData sheetId="2970"/>
-      <sheetData sheetId="2971"/>
-      <sheetData sheetId="2972"/>
-      <sheetData sheetId="2973"/>
+      <sheetData sheetId="2965" refreshError="1"/>
+      <sheetData sheetId="2966" refreshError="1"/>
+      <sheetData sheetId="2967" refreshError="1"/>
+      <sheetData sheetId="2968" refreshError="1"/>
+      <sheetData sheetId="2969" refreshError="1"/>
+      <sheetData sheetId="2970" refreshError="1"/>
+      <sheetData sheetId="2971" refreshError="1"/>
+      <sheetData sheetId="2972" refreshError="1"/>
+      <sheetData sheetId="2973" refreshError="1"/>
       <sheetData sheetId="2974" refreshError="1"/>
       <sheetData sheetId="2975"/>
       <sheetData sheetId="2976" refreshError="1"/>
@@ -20955,6 +21480,326 @@
       <sheetData sheetId="2982" refreshError="1"/>
       <sheetData sheetId="2983" refreshError="1"/>
       <sheetData sheetId="2984" refreshError="1"/>
+      <sheetData sheetId="2985" refreshError="1"/>
+      <sheetData sheetId="2986" refreshError="1"/>
+      <sheetData sheetId="2987" refreshError="1"/>
+      <sheetData sheetId="2988" refreshError="1"/>
+      <sheetData sheetId="2989" refreshError="1"/>
+      <sheetData sheetId="2990" refreshError="1"/>
+      <sheetData sheetId="2991" refreshError="1"/>
+      <sheetData sheetId="2992" refreshError="1"/>
+      <sheetData sheetId="2993" refreshError="1"/>
+      <sheetData sheetId="2994" refreshError="1"/>
+      <sheetData sheetId="2995" refreshError="1"/>
+      <sheetData sheetId="2996" refreshError="1"/>
+      <sheetData sheetId="2997" refreshError="1"/>
+      <sheetData sheetId="2998" refreshError="1"/>
+      <sheetData sheetId="2999" refreshError="1"/>
+      <sheetData sheetId="3000" refreshError="1"/>
+      <sheetData sheetId="3001" refreshError="1"/>
+      <sheetData sheetId="3002" refreshError="1"/>
+      <sheetData sheetId="3003" refreshError="1"/>
+      <sheetData sheetId="3004" refreshError="1"/>
+      <sheetData sheetId="3005" refreshError="1"/>
+      <sheetData sheetId="3006" refreshError="1"/>
+      <sheetData sheetId="3007" refreshError="1"/>
+      <sheetData sheetId="3008" refreshError="1"/>
+      <sheetData sheetId="3009" refreshError="1"/>
+      <sheetData sheetId="3010" refreshError="1"/>
+      <sheetData sheetId="3011" refreshError="1"/>
+      <sheetData sheetId="3012" refreshError="1"/>
+      <sheetData sheetId="3013" refreshError="1"/>
+      <sheetData sheetId="3014" refreshError="1"/>
+      <sheetData sheetId="3015" refreshError="1"/>
+      <sheetData sheetId="3016" refreshError="1"/>
+      <sheetData sheetId="3017" refreshError="1"/>
+      <sheetData sheetId="3018" refreshError="1"/>
+      <sheetData sheetId="3019" refreshError="1"/>
+      <sheetData sheetId="3020" refreshError="1"/>
+      <sheetData sheetId="3021" refreshError="1"/>
+      <sheetData sheetId="3022" refreshError="1"/>
+      <sheetData sheetId="3023" refreshError="1"/>
+      <sheetData sheetId="3024" refreshError="1"/>
+      <sheetData sheetId="3025" refreshError="1"/>
+      <sheetData sheetId="3026" refreshError="1"/>
+      <sheetData sheetId="3027" refreshError="1"/>
+      <sheetData sheetId="3028" refreshError="1"/>
+      <sheetData sheetId="3029" refreshError="1"/>
+      <sheetData sheetId="3030" refreshError="1"/>
+      <sheetData sheetId="3031" refreshError="1"/>
+      <sheetData sheetId="3032" refreshError="1"/>
+      <sheetData sheetId="3033" refreshError="1"/>
+      <sheetData sheetId="3034"/>
+      <sheetData sheetId="3035"/>
+      <sheetData sheetId="3036"/>
+      <sheetData sheetId="3037"/>
+      <sheetData sheetId="3038"/>
+      <sheetData sheetId="3039"/>
+      <sheetData sheetId="3040"/>
+      <sheetData sheetId="3041"/>
+      <sheetData sheetId="3042"/>
+      <sheetData sheetId="3043"/>
+      <sheetData sheetId="3044"/>
+      <sheetData sheetId="3045"/>
+      <sheetData sheetId="3046"/>
+      <sheetData sheetId="3047"/>
+      <sheetData sheetId="3048"/>
+      <sheetData sheetId="3049"/>
+      <sheetData sheetId="3050"/>
+      <sheetData sheetId="3051"/>
+      <sheetData sheetId="3052"/>
+      <sheetData sheetId="3053"/>
+      <sheetData sheetId="3054"/>
+      <sheetData sheetId="3055"/>
+      <sheetData sheetId="3056"/>
+      <sheetData sheetId="3057"/>
+      <sheetData sheetId="3058"/>
+      <sheetData sheetId="3059"/>
+      <sheetData sheetId="3060"/>
+      <sheetData sheetId="3061"/>
+      <sheetData sheetId="3062"/>
+      <sheetData sheetId="3063"/>
+      <sheetData sheetId="3064"/>
+      <sheetData sheetId="3065"/>
+      <sheetData sheetId="3066"/>
+      <sheetData sheetId="3067"/>
+      <sheetData sheetId="3068"/>
+      <sheetData sheetId="3069"/>
+      <sheetData sheetId="3070"/>
+      <sheetData sheetId="3071"/>
+      <sheetData sheetId="3072"/>
+      <sheetData sheetId="3073"/>
+      <sheetData sheetId="3074"/>
+      <sheetData sheetId="3075"/>
+      <sheetData sheetId="3076"/>
+      <sheetData sheetId="3077">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3078">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3079">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3080">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3081">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3082">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3083">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3084">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3085">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3086">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3087">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3088">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3089">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3090">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3091">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3092">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3093">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3094">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3095">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3096">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3097">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3098">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3099">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3100"/>
+      <sheetData sheetId="3101"/>
+      <sheetData sheetId="3102"/>
+      <sheetData sheetId="3103"/>
+      <sheetData sheetId="3104"/>
+      <sheetData sheetId="3105"/>
+      <sheetData sheetId="3106"/>
+      <sheetData sheetId="3107"/>
+      <sheetData sheetId="3108"/>
+      <sheetData sheetId="3109"/>
+      <sheetData sheetId="3110"/>
+      <sheetData sheetId="3111"/>
+      <sheetData sheetId="3112"/>
+      <sheetData sheetId="3113"/>
+      <sheetData sheetId="3114"/>
+      <sheetData sheetId="3115"/>
+      <sheetData sheetId="3116"/>
+      <sheetData sheetId="3117"/>
+      <sheetData sheetId="3118"/>
+      <sheetData sheetId="3119"/>
+      <sheetData sheetId="3120"/>
+      <sheetData sheetId="3121"/>
+      <sheetData sheetId="3122"/>
+      <sheetData sheetId="3123"/>
+      <sheetData sheetId="3124"/>
+      <sheetData sheetId="3125"/>
+      <sheetData sheetId="3126"/>
+      <sheetData sheetId="3127"/>
+      <sheetData sheetId="3128"/>
+      <sheetData sheetId="3129"/>
+      <sheetData sheetId="3130"/>
+      <sheetData sheetId="3131"/>
+      <sheetData sheetId="3132"/>
+      <sheetData sheetId="3133"/>
+      <sheetData sheetId="3134"/>
+      <sheetData sheetId="3135"/>
+      <sheetData sheetId="3136"/>
+      <sheetData sheetId="3137" refreshError="1"/>
+      <sheetData sheetId="3138" refreshError="1"/>
+      <sheetData sheetId="3139" refreshError="1"/>
+      <sheetData sheetId="3140" refreshError="1"/>
+      <sheetData sheetId="3141" refreshError="1"/>
+      <sheetData sheetId="3142" refreshError="1"/>
+      <sheetData sheetId="3143" refreshError="1"/>
+      <sheetData sheetId="3144" refreshError="1"/>
+      <sheetData sheetId="3145" refreshError="1"/>
+      <sheetData sheetId="3146" refreshError="1"/>
+      <sheetData sheetId="3147" refreshError="1"/>
+      <sheetData sheetId="3148" refreshError="1"/>
+      <sheetData sheetId="3149" refreshError="1"/>
+      <sheetData sheetId="3150" refreshError="1"/>
+      <sheetData sheetId="3151" refreshError="1"/>
+      <sheetData sheetId="3152" refreshError="1"/>
+      <sheetData sheetId="3153" refreshError="1"/>
+      <sheetData sheetId="3154" refreshError="1"/>
+      <sheetData sheetId="3155" refreshError="1"/>
+      <sheetData sheetId="3156" refreshError="1"/>
+      <sheetData sheetId="3157" refreshError="1"/>
+      <sheetData sheetId="3158" refreshError="1"/>
+      <sheetData sheetId="3159" refreshError="1"/>
+      <sheetData sheetId="3160" refreshError="1"/>
+      <sheetData sheetId="3161" refreshError="1"/>
+      <sheetData sheetId="3162" refreshError="1"/>
+      <sheetData sheetId="3163" refreshError="1"/>
+      <sheetData sheetId="3164" refreshError="1"/>
+      <sheetData sheetId="3165" refreshError="1"/>
+      <sheetData sheetId="3166" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -21049,17 +21894,66 @@
       <sheetName val="_UnderConst_Analysis"/>
       <sheetName val="アップロード系(2)"/>
       <sheetName val="List"/>
+      <sheetName val="パラメータ設定表"/>
       <sheetName val="別紙7_操作系イベント発生時_"/>
       <sheetName val="別紙11_各競合条件における起動可否_"/>
       <sheetName val="index"/>
-      <sheetName val="パラメータ設定表"/>
+      <sheetName val="入力"/>
+      <sheetName val="415T戟L"/>
+      <sheetName val="No.31"/>
       <sheetName val="改訂履歴"/>
       <sheetName val="リスト"/>
       <sheetName val="ドメイン"/>
       <sheetName val="format"/>
-      <sheetName val="入力"/>
-      <sheetName val="415T戟L"/>
-      <sheetName val="No.31"/>
+      <sheetName val="Navigation"/>
+      <sheetName val="Cover"/>
+      <sheetName val="DataList"/>
+      <sheetName val="変更要件"/>
+      <sheetName val="【石倉編集中】DisplayStateTransitionTa"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="Calcul"/>
+      <sheetName val="Data"/>
+      <sheetName val="★VarUsed"/>
+      <sheetName val="輝度計算(直線用)"/>
+      <sheetName val="コード_dimautocon"/>
+      <sheetName val="パラメータ_dimautocon"/>
+      <sheetName val="パラメータ_dimcalprcnt"/>
+      <sheetName val="パラメータ_dimmanualstep"/>
+      <sheetName val="パラメータ_dimmgr"/>
+      <sheetName val="XX-0080"/>
+      <sheetName val="メッセージ定義"/>
+      <sheetName val="XX-0180"/>
+      <sheetName val="lock"/>
+      <sheetName val="level"/>
+      <sheetName val="cominf"/>
+      <sheetName val="disconnect"/>
+      <sheetName val="９ｘ"/>
+      <sheetName val="Ｂｘ"/>
+      <sheetName val="Ｃｘ"/>
+      <sheetName val="Ｅｘ"/>
+      <sheetName val="休日"/>
+      <sheetName val="HMI-004_Screen（old）"/>
+      <sheetName val="ﾊﾟｲﾌﾟ"/>
+      <sheetName val="冷延鋼板"/>
+      <sheetName val="熱延鋼板"/>
+      <sheetName val="他材料費"/>
+      <sheetName val="MOTO"/>
+      <sheetName val="前提書情報"/>
+      <sheetName val="②P071中計　工数パターン1312更新"/>
+      <sheetName val="module"/>
+      <sheetName val="選択肢"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="メニュー"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="R0-10表紙MIC"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="修正ﾌｧｲﾙ一覧"/>
+      <sheetName val="RGB"/>
+      <sheetName val="415T原"/>
+      <sheetName val="工数ｺｰﾄﾞﾘｽﾄ"/>
+      <sheetName val="Setting_Check"/>
+      <sheetName val="用語集"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -21158,6 +22052,55 @@
       <sheetData sheetId="93" refreshError="1"/>
       <sheetData sheetId="94" refreshError="1"/>
       <sheetData sheetId="95" refreshError="1"/>
+      <sheetData sheetId="96" refreshError="1"/>
+      <sheetData sheetId="97" refreshError="1"/>
+      <sheetData sheetId="98" refreshError="1"/>
+      <sheetData sheetId="99" refreshError="1"/>
+      <sheetData sheetId="100" refreshError="1"/>
+      <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
+      <sheetData sheetId="133" refreshError="1"/>
+      <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
+      <sheetData sheetId="141" refreshError="1"/>
+      <sheetData sheetId="142" refreshError="1"/>
+      <sheetData sheetId="143" refreshError="1"/>
+      <sheetData sheetId="144" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -21454,10 +22397,10 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="C1:AM57"/>
-  <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.08984375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="52" width="2.125" style="218" customWidth="1"/>
-    <col min="53" max="16384" width="8.125" style="218"/>
+    <col min="1" max="52" width="2.08984375" style="218" customWidth="1"/>
+    <col min="53" max="16384" width="8.08984375" style="218"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:20" ht="13.15" customHeight="1"/>
@@ -21515,32 +22458,32 @@
       <c r="AJ33" s="222"/>
     </row>
     <row r="34" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y34" s="221" t="s">
-        <v>333</v>
+      <c r="Y34" s="150" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="35" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y35" s="234" t="s">
-        <v>334</v>
-      </c>
-      <c r="Z35" s="235"/>
-      <c r="AA35" s="235"/>
-      <c r="AB35" s="235"/>
-      <c r="AC35" s="236"/>
-      <c r="AD35" s="234" t="s">
-        <v>335</v>
-      </c>
-      <c r="AE35" s="235"/>
-      <c r="AF35" s="235"/>
-      <c r="AG35" s="235"/>
-      <c r="AH35" s="236"/>
-      <c r="AI35" s="234" t="s">
-        <v>336</v>
-      </c>
-      <c r="AJ35" s="235"/>
-      <c r="AK35" s="235"/>
-      <c r="AL35" s="235"/>
-      <c r="AM35" s="236"/>
+      <c r="Y35" s="239" t="s">
+        <v>331</v>
+      </c>
+      <c r="Z35" s="240"/>
+      <c r="AA35" s="240"/>
+      <c r="AB35" s="240"/>
+      <c r="AC35" s="241"/>
+      <c r="AD35" s="239" t="s">
+        <v>332</v>
+      </c>
+      <c r="AE35" s="240"/>
+      <c r="AF35" s="240"/>
+      <c r="AG35" s="240"/>
+      <c r="AH35" s="241"/>
+      <c r="AI35" s="239" t="s">
+        <v>333</v>
+      </c>
+      <c r="AJ35" s="240"/>
+      <c r="AK35" s="240"/>
+      <c r="AL35" s="240"/>
+      <c r="AM35" s="241"/>
     </row>
     <row r="36" spans="3:39" ht="13.15" customHeight="1">
       <c r="D36" s="222"/>
@@ -21586,21 +22529,21 @@
       <c r="Y38" s="227"/>
       <c r="Z38" s="222"/>
       <c r="AA38" s="223" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AB38" s="222"/>
       <c r="AC38" s="229"/>
       <c r="AD38" s="227"/>
       <c r="AE38" s="222"/>
       <c r="AF38" s="223" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AG38" s="222"/>
       <c r="AH38" s="229"/>
       <c r="AI38" s="230"/>
       <c r="AJ38" s="222"/>
       <c r="AK38" s="223" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AL38" s="222"/>
       <c r="AM38" s="229"/>
@@ -21635,31 +22578,31 @@
     <row r="41" spans="3:39" ht="13.15" customHeight="1"/>
     <row r="42" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y42" s="221" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="43" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y43" s="234" t="s">
-        <v>334</v>
-      </c>
-      <c r="Z43" s="235"/>
-      <c r="AA43" s="235"/>
-      <c r="AB43" s="235"/>
-      <c r="AC43" s="236"/>
-      <c r="AD43" s="234" t="s">
-        <v>335</v>
-      </c>
-      <c r="AE43" s="235"/>
-      <c r="AF43" s="235"/>
-      <c r="AG43" s="235"/>
-      <c r="AH43" s="236"/>
-      <c r="AI43" s="234" t="s">
-        <v>336</v>
-      </c>
-      <c r="AJ43" s="235"/>
-      <c r="AK43" s="235"/>
-      <c r="AL43" s="235"/>
-      <c r="AM43" s="236"/>
+      <c r="Y43" s="239" t="s">
+        <v>331</v>
+      </c>
+      <c r="Z43" s="240"/>
+      <c r="AA43" s="240"/>
+      <c r="AB43" s="240"/>
+      <c r="AC43" s="241"/>
+      <c r="AD43" s="239" t="s">
+        <v>332</v>
+      </c>
+      <c r="AE43" s="240"/>
+      <c r="AF43" s="240"/>
+      <c r="AG43" s="240"/>
+      <c r="AH43" s="241"/>
+      <c r="AI43" s="239" t="s">
+        <v>333</v>
+      </c>
+      <c r="AJ43" s="240"/>
+      <c r="AK43" s="240"/>
+      <c r="AL43" s="240"/>
+      <c r="AM43" s="241"/>
     </row>
     <row r="44" spans="3:39" ht="13.15" customHeight="1">
       <c r="D44" s="222"/>
@@ -21705,21 +22648,21 @@
       <c r="Y46" s="227"/>
       <c r="Z46" s="222"/>
       <c r="AA46" s="223" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AB46" s="222"/>
       <c r="AC46" s="229"/>
       <c r="AD46" s="222"/>
       <c r="AE46" s="222"/>
       <c r="AF46" s="223" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AG46" s="222"/>
       <c r="AH46" s="229"/>
       <c r="AI46" s="230"/>
       <c r="AJ46" s="222"/>
       <c r="AK46" s="223" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AL46" s="222"/>
       <c r="AM46" s="229"/>
@@ -21753,31 +22696,31 @@
     <row r="49" spans="4:39" ht="13.15" customHeight="1"/>
     <row r="50" spans="4:39" ht="13.15" customHeight="1">
       <c r="Y50" s="221" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="51" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y51" s="234" t="s">
-        <v>334</v>
-      </c>
-      <c r="Z51" s="235"/>
-      <c r="AA51" s="235"/>
-      <c r="AB51" s="235"/>
-      <c r="AC51" s="236"/>
-      <c r="AD51" s="234" t="s">
-        <v>335</v>
-      </c>
-      <c r="AE51" s="235"/>
-      <c r="AF51" s="235"/>
-      <c r="AG51" s="235"/>
-      <c r="AH51" s="236"/>
-      <c r="AI51" s="234" t="s">
-        <v>336</v>
-      </c>
-      <c r="AJ51" s="235"/>
-      <c r="AK51" s="235"/>
-      <c r="AL51" s="235"/>
-      <c r="AM51" s="236"/>
+      <c r="Y51" s="239" t="s">
+        <v>331</v>
+      </c>
+      <c r="Z51" s="240"/>
+      <c r="AA51" s="240"/>
+      <c r="AB51" s="240"/>
+      <c r="AC51" s="241"/>
+      <c r="AD51" s="239" t="s">
+        <v>332</v>
+      </c>
+      <c r="AE51" s="240"/>
+      <c r="AF51" s="240"/>
+      <c r="AG51" s="240"/>
+      <c r="AH51" s="241"/>
+      <c r="AI51" s="239" t="s">
+        <v>333</v>
+      </c>
+      <c r="AJ51" s="240"/>
+      <c r="AK51" s="240"/>
+      <c r="AL51" s="240"/>
+      <c r="AM51" s="241"/>
     </row>
     <row r="52" spans="4:39" ht="13.15" customHeight="1">
       <c r="D52" s="222"/>
@@ -21823,21 +22766,21 @@
       <c r="Y54" s="227"/>
       <c r="Z54" s="222"/>
       <c r="AA54" s="223" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AB54" s="222"/>
       <c r="AC54" s="229"/>
       <c r="AD54" s="222"/>
       <c r="AE54" s="222"/>
       <c r="AF54" s="223" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AG54" s="222"/>
       <c r="AH54" s="229"/>
       <c r="AI54" s="230"/>
       <c r="AJ54" s="222"/>
       <c r="AK54" s="223" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AL54" s="222"/>
       <c r="AM54" s="229"/>
@@ -21868,7 +22811,7 @@
     </row>
     <row r="57" spans="4:39" ht="13.15" customHeight="1">
       <c r="AK57" s="218" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -21894,14 +22837,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
+    <col min="1" max="1" width="4.36328125" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.375" customWidth="1"/>
-    <col min="5" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="18" width="13.125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="69.36328125" customWidth="1"/>
+    <col min="5" max="6" width="12.7265625" customWidth="1"/>
+    <col min="7" max="18" width="13.08984375" hidden="1" customWidth="1"/>
     <col min="19" max="22" width="0" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="11" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -21912,18 +22857,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="245" t="s">
+      <c r="I2" s="242" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="245"/>
-      <c r="K2" s="245"/>
-      <c r="L2" s="245"/>
-      <c r="M2" s="245"/>
-      <c r="N2" s="245"/>
-      <c r="O2" s="245"/>
-      <c r="P2" s="245"/>
-      <c r="Q2" s="245"/>
-      <c r="R2" s="245"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="M2" s="242"/>
+      <c r="N2" s="242"/>
+      <c r="O2" s="242"/>
+      <c r="P2" s="242"/>
+      <c r="Q2" s="242"/>
+      <c r="R2" s="242"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -21936,25 +22881,25 @@
       <c r="H3" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="I3" s="246" t="s">
+      <c r="I3" s="243" t="s">
         <v>183</v>
       </c>
-      <c r="J3" s="247"/>
-      <c r="K3" s="247"/>
-      <c r="L3" s="247"/>
-      <c r="M3" s="247"/>
-      <c r="N3" s="247"/>
-      <c r="O3" s="247"/>
-      <c r="P3" s="247"/>
-      <c r="Q3" s="247"/>
-      <c r="R3" s="247"/>
+      <c r="J3" s="244"/>
+      <c r="K3" s="244"/>
+      <c r="L3" s="244"/>
+      <c r="M3" s="244"/>
+      <c r="N3" s="244"/>
+      <c r="O3" s="244"/>
+      <c r="P3" s="244"/>
+      <c r="Q3" s="244"/>
+      <c r="R3" s="244"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="22" t="str">
         <f>DGET(B8:C14,"Ver.",H4:H5)</f>
-        <v>1.0.1</v>
+        <v>1.0.2</v>
       </c>
       <c r="F4" s="6"/>
       <c r="H4" s="9" t="s">
@@ -21968,45 +22913,45 @@
       <c r="F5" s="6"/>
       <c r="H5" s="11">
         <f>MAX(B9:B14)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" ht="13.5" thickBot="1"/>
+    <row r="7" spans="2:24">
+      <c r="C7" s="247" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="248"/>
+      <c r="E7" s="249" t="s">
         <v>2</v>
       </c>
+      <c r="F7" s="249"/>
+      <c r="G7" s="250" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="250"/>
+      <c r="I7" s="250"/>
+      <c r="J7" s="250"/>
+      <c r="K7" s="250"/>
+      <c r="L7" s="250"/>
+      <c r="M7" s="251" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="251"/>
+      <c r="O7" s="251"/>
+      <c r="P7" s="251"/>
+      <c r="Q7" s="251"/>
+      <c r="R7" s="252"/>
+      <c r="S7" s="245" t="s">
+        <v>324</v>
+      </c>
+      <c r="T7" s="245"/>
+      <c r="U7" s="245"/>
+      <c r="V7" s="245"/>
+      <c r="W7" s="245"/>
+      <c r="X7" s="246"/>
     </row>
-    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
-    <row r="7" spans="2:24">
-      <c r="C7" s="239" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="240"/>
-      <c r="E7" s="241" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="241"/>
-      <c r="G7" s="242" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="242"/>
-      <c r="I7" s="242"/>
-      <c r="J7" s="242"/>
-      <c r="K7" s="242"/>
-      <c r="L7" s="242"/>
-      <c r="M7" s="243" t="s">
-        <v>12</v>
-      </c>
-      <c r="N7" s="243"/>
-      <c r="O7" s="243"/>
-      <c r="P7" s="243"/>
-      <c r="Q7" s="243"/>
-      <c r="R7" s="244"/>
-      <c r="S7" s="237" t="s">
-        <v>326</v>
-      </c>
-      <c r="T7" s="237"/>
-      <c r="U7" s="237"/>
-      <c r="V7" s="237"/>
-      <c r="W7" s="237"/>
-      <c r="X7" s="238"/>
-    </row>
-    <row r="8" spans="2:24" ht="27.75" thickBot="1">
+    <row r="8" spans="2:24" ht="26.5" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>15</v>
       </c>
@@ -22059,7 +23004,7 @@
         <v>11</v>
       </c>
       <c r="S8" s="16" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="T8" s="16" t="s">
         <v>7</v>
@@ -22077,22 +23022,22 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="122.25" thickTop="1">
+    <row r="9" spans="2:24" ht="117.5" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D9" s="213" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>31</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>31</v>
@@ -22125,7 +23070,7 @@
         <v>31</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="R9" s="216">
         <v>44279</v>
@@ -22149,16 +23094,16 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="40.5">
+    <row r="10" spans="2:24" ht="39">
       <c r="B10" s="9">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D10" s="211" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>31</v>
@@ -22215,21 +23160,29 @@
         <v>31</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="X10" s="212">
         <v>45811</v>
       </c>
     </row>
-    <row r="11" spans="2:24">
+    <row r="11" spans="2:24" ht="117">
       <c r="B11" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="C11" s="234" t="s">
+        <v>348</v>
+      </c>
+      <c r="D11" s="235" t="s">
+        <v>351</v>
+      </c>
+      <c r="E11" s="236" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="236" t="s">
+        <v>31</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -22246,8 +23199,12 @@
       <c r="T11" s="216"/>
       <c r="U11" s="1"/>
       <c r="V11" s="216"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="212"/>
+      <c r="W11" s="237" t="s">
+        <v>349</v>
+      </c>
+      <c r="X11" s="238">
+        <v>46009</v>
+      </c>
     </row>
     <row r="12" spans="2:24">
       <c r="B12" s="9">
@@ -22277,7 +23234,7 @@
       <c r="W12" s="1"/>
       <c r="X12" s="212"/>
     </row>
-    <row r="13" spans="2:24" ht="14.25" thickBot="1">
+    <row r="13" spans="2:24" ht="13.5" thickBot="1">
       <c r="B13" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -22331,11 +23288,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="4.625" customWidth="1"/>
-    <col min="3" max="3" width="3.375" customWidth="1"/>
-    <col min="4" max="4" width="17.375" customWidth="1"/>
+    <col min="2" max="2" width="4.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.36328125" customWidth="1"/>
+    <col min="4" max="4" width="17.36328125" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22349,13 +23306,13 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14.25" thickBot="1">
+    <row r="6" spans="2:5" ht="13.5" thickBot="1">
       <c r="B6" s="150" t="s">
         <v>128</v>
       </c>
       <c r="C6" s="150"/>
     </row>
-    <row r="7" spans="2:5" ht="14.25" thickBot="1">
+    <row r="7" spans="2:5" ht="13.5" thickBot="1">
       <c r="C7" s="78" t="s">
         <v>130</v>
       </c>
@@ -22375,7 +23332,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="27">
+    <row r="9" spans="2:5" ht="26">
       <c r="C9" s="160">
         <v>1</v>
       </c>
@@ -22386,7 +23343,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="14.25" thickBot="1">
+    <row r="10" spans="2:5" ht="13.5" thickBot="1">
       <c r="C10" s="158"/>
       <c r="D10" s="89"/>
       <c r="E10" s="5"/>
@@ -22394,14 +23351,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="156"/>
     </row>
-    <row r="12" spans="2:5" ht="14.25" thickBot="1">
+    <row r="12" spans="2:5" ht="13.5" thickBot="1">
       <c r="B12" s="151" t="s">
         <v>129</v>
       </c>
       <c r="C12" s="85"/>
       <c r="D12" s="85"/>
     </row>
-    <row r="13" spans="2:5" ht="14.25" thickBot="1">
+    <row r="13" spans="2:5" ht="13.5" thickBot="1">
       <c r="B13" s="152"/>
       <c r="C13" s="157" t="s">
         <v>130</v>
@@ -22413,7 +23370,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="14.25" thickTop="1">
+    <row r="14" spans="2:5" ht="13.5" thickTop="1">
       <c r="C14" s="154">
         <v>0</v>
       </c>
@@ -22490,17 +23447,17 @@
         <v>177</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="14.25" thickBot="1">
+    <row r="21" spans="2:5" ht="13.5" thickBot="1">
       <c r="C21" s="158"/>
       <c r="D21" s="89"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="14.25" thickBot="1">
+    <row r="24" spans="2:5" ht="13.5" thickBot="1">
       <c r="B24" s="150" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="14.25" thickBot="1">
+    <row r="25" spans="2:5" ht="13.5" thickBot="1">
       <c r="C25" s="157" t="s">
         <v>130</v>
       </c>
@@ -22587,26 +23544,26 @@
       <c r="D33" s="88"/>
       <c r="E33" s="77"/>
     </row>
-    <row r="34" spans="2:5" ht="14.25" thickBot="1">
+    <row r="34" spans="2:5" ht="13.5" thickBot="1">
       <c r="C34" s="158"/>
       <c r="D34" s="89"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="14.25" thickBot="1">
+    <row r="37" spans="2:5" ht="13.5" thickBot="1">
       <c r="B37" s="150" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="248"/>
-      <c r="D38" s="249"/>
+      <c r="C38" s="253"/>
+      <c r="D38" s="254"/>
       <c r="E38" s="114" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="14.25" thickBot="1">
-      <c r="C39" s="250"/>
-      <c r="D39" s="251"/>
+    <row r="39" spans="2:5" ht="13.5" thickBot="1">
+      <c r="C39" s="255"/>
+      <c r="D39" s="256"/>
       <c r="E39" s="5" t="s">
         <v>119</v>
       </c>
@@ -22635,131 +23592,131 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.75" customWidth="1"/>
-    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.7265625" customWidth="1"/>
+    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="264" t="s">
+      <c r="B2" s="269" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="265"/>
-      <c r="D2" s="252" t="s">
-        <v>323</v>
-      </c>
-      <c r="E2" s="253"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="253"/>
-      <c r="H2" s="254"/>
+      <c r="C2" s="270"/>
+      <c r="D2" s="257" t="s">
+        <v>321</v>
+      </c>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="266" t="s">
+      <c r="B3" s="271" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="267"/>
-      <c r="D3" s="270" t="s">
-        <v>324</v>
-      </c>
-      <c r="E3" s="271"/>
-      <c r="F3" s="271"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="272"/>
+      <c r="C3" s="272"/>
+      <c r="D3" s="275" t="s">
+        <v>322</v>
+      </c>
+      <c r="E3" s="276"/>
+      <c r="F3" s="276"/>
+      <c r="G3" s="276"/>
+      <c r="H3" s="277"/>
     </row>
-    <row r="4" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B4" s="268" t="s">
+    <row r="4" spans="2:14" ht="13.5" thickBot="1">
+      <c r="B4" s="273" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="269"/>
-      <c r="D4" s="255" t="str">
+      <c r="C4" s="274"/>
+      <c r="D4" s="260" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_O_CHAMAL-CSTD-0-00-C-C0.c</v>
       </c>
-      <c r="E4" s="256"/>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
-      <c r="H4" s="257"/>
+      <c r="E4" s="261"/>
+      <c r="F4" s="261"/>
+      <c r="G4" s="261"/>
+      <c r="H4" s="262"/>
     </row>
-    <row r="5" spans="2:14" ht="14.25" thickBot="1">
+    <row r="5" spans="2:14" ht="13.5" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="264" t="s">
+      <c r="B6" s="269" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="265"/>
-      <c r="D6" s="258" t="str">
+      <c r="C6" s="270"/>
+      <c r="D6" s="263" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>O_CHAMAL</v>
       </c>
-      <c r="E6" s="259"/>
-      <c r="F6" s="259"/>
-      <c r="G6" s="259"/>
-      <c r="H6" s="260"/>
+      <c r="E6" s="264"/>
+      <c r="F6" s="264"/>
+      <c r="G6" s="264"/>
+      <c r="H6" s="265"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="266" t="s">
+      <c r="B7" s="271" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="267"/>
-      <c r="D7" s="261">
+      <c r="C7" s="272"/>
+      <c r="D7" s="266">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="262"/>
-      <c r="F7" s="262"/>
-      <c r="G7" s="262"/>
-      <c r="H7" s="263"/>
+      <c r="E7" s="267"/>
+      <c r="F7" s="267"/>
+      <c r="G7" s="267"/>
+      <c r="H7" s="268"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="266" t="s">
+      <c r="B8" s="271" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="267"/>
-      <c r="D8" s="261" t="str">
+      <c r="C8" s="272"/>
+      <c r="D8" s="266" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_O_CHAMAL_MTRX</v>
       </c>
-      <c r="E8" s="262"/>
-      <c r="F8" s="262"/>
-      <c r="G8" s="262"/>
-      <c r="H8" s="263"/>
+      <c r="E8" s="267"/>
+      <c r="F8" s="267"/>
+      <c r="G8" s="267"/>
+      <c r="H8" s="268"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="266" t="s">
+      <c r="B9" s="271" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="267"/>
-      <c r="D9" s="273" t="s">
+      <c r="C9" s="272"/>
+      <c r="D9" s="278" t="s">
         <v>215</v>
       </c>
-      <c r="E9" s="274"/>
-      <c r="F9" s="274"/>
-      <c r="G9" s="274"/>
-      <c r="H9" s="275"/>
+      <c r="E9" s="279"/>
+      <c r="F9" s="279"/>
+      <c r="G9" s="279"/>
+      <c r="H9" s="280"/>
     </row>
-    <row r="10" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B10" s="268" t="s">
+    <row r="10" spans="2:14" ht="13.5" thickBot="1">
+      <c r="B10" s="273" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="269"/>
-      <c r="D10" s="276"/>
-      <c r="E10" s="277"/>
-      <c r="F10" s="277"/>
-      <c r="G10" s="277"/>
-      <c r="H10" s="278"/>
+      <c r="C10" s="274"/>
+      <c r="D10" s="281"/>
+      <c r="E10" s="282"/>
+      <c r="F10" s="282"/>
+      <c r="G10" s="282"/>
+      <c r="H10" s="283"/>
     </row>
-    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
-    <row r="12" spans="2:14" ht="14.25" thickBot="1">
+    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.5" thickBot="1">
       <c r="B12" s="141" t="s">
         <v>34</v>
       </c>
@@ -22794,7 +23751,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="14.25" thickTop="1">
+    <row r="13" spans="2:14" ht="13.5" thickTop="1">
       <c r="B13" s="107">
         <v>1</v>
       </c>
@@ -22805,15 +23762,15 @@
         <v>48</v>
       </c>
       <c r="E13" s="113" t="s">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="F13" s="53" t="str">
         <f t="shared" ref="F13:F37" ca="1" si="0">IF($D13&lt;&gt;"","u4_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"Srcchk","")</f>
         <v>u4_s_AlertO_chamalSrcchk</v>
       </c>
       <c r="G13" s="53" t="str">
-        <f t="shared" ref="G13:G37" ca="1" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
-        <v>vd_s_AlertO_chamalRwTx</v>
+        <f t="shared" ref="G13:G37" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
+        <v>NULL</v>
       </c>
       <c r="H13" s="111" t="str">
         <f ca="1">IF($D13&lt;&gt;"","ALERT_CH_"&amp;UPPER($D$6)&amp;IF($D$7=1,"","_"&amp;UPPER($C13)),"")</f>
@@ -23647,7 +24604,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="14.25" thickBot="1">
+    <row r="37" spans="2:14" ht="13.5" thickBot="1">
       <c r="B37" s="98">
         <v>25</v>
       </c>
@@ -23750,21 +24707,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.375" customWidth="1"/>
-    <col min="6" max="6" width="52.75" customWidth="1"/>
-    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.875" customWidth="1"/>
-    <col min="16" max="16" width="9.875" customWidth="1"/>
-    <col min="17" max="17" width="44.625" customWidth="1"/>
-    <col min="18" max="18" width="73.625" customWidth="1"/>
+    <col min="5" max="5" width="36.36328125" customWidth="1"/>
+    <col min="6" max="6" width="52.7265625" customWidth="1"/>
+    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.90625" customWidth="1"/>
+    <col min="16" max="16" width="9.90625" customWidth="1"/>
+    <col min="17" max="17" width="44.6328125" customWidth="1"/>
+    <col min="18" max="18" width="73.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="14.25" thickBot="1">
+    <row r="2" spans="2:18" ht="13.5" thickBot="1">
       <c r="B2" t="s">
         <v>200</v>
       </c>
@@ -23772,7 +24729,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="14.25" thickBot="1">
+    <row r="3" spans="2:18" ht="13.5" thickBot="1">
       <c r="B3" s="141" t="s">
         <v>34</v>
       </c>
@@ -23810,7 +24767,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
       <c r="B4" s="173">
         <v>0</v>
       </c>
@@ -23838,7 +24795,7 @@
       </c>
       <c r="R4" s="140"/>
     </row>
-    <row r="5" spans="2:18" ht="14.25" thickTop="1">
+    <row r="5" spans="2:18" ht="13.5" thickTop="1">
       <c r="B5" s="176">
         <v>1</v>
       </c>
@@ -24366,7 +25323,7 @@
       <c r="Q28" s="145"/>
       <c r="R28" s="119"/>
     </row>
-    <row r="29" spans="2:18" ht="14.25" thickBot="1">
+    <row r="29" spans="2:18" ht="13.5" thickBot="1">
       <c r="B29" s="177">
         <v>25</v>
       </c>
@@ -24388,7 +25345,7 @@
       <c r="Q29" s="143"/>
       <c r="R29" s="121"/>
     </row>
-    <row r="32" spans="2:18" ht="14.25" thickBot="1">
+    <row r="32" spans="2:18" ht="13.5" thickBot="1">
       <c r="B32" t="s">
         <v>201</v>
       </c>
@@ -24396,7 +25353,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="14.25" thickBot="1">
+    <row r="33" spans="2:18" ht="13.5" thickBot="1">
       <c r="B33" s="141" t="s">
         <v>34</v>
       </c>
@@ -24428,7 +25385,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
       <c r="B34" s="173">
         <v>0</v>
       </c>
@@ -24454,7 +25411,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="14.25" thickTop="1">
+    <row r="35" spans="2:18" ht="13.5" thickTop="1">
       <c r="B35" s="176">
         <v>1</v>
       </c>
@@ -24982,7 +25939,7 @@
       <c r="Q58" s="145"/>
       <c r="R58" s="178"/>
     </row>
-    <row r="59" spans="2:18" ht="14.25" thickBot="1">
+    <row r="59" spans="2:18" ht="13.5" thickBot="1">
       <c r="B59" s="177">
         <v>25</v>
       </c>
@@ -25033,29 +25990,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="28.375" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="5" max="5" width="12.375" customWidth="1"/>
-    <col min="6" max="6" width="19.75" customWidth="1"/>
-    <col min="7" max="7" width="12.375" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="12.375" customWidth="1"/>
-    <col min="10" max="10" width="35.125" customWidth="1"/>
-    <col min="11" max="11" width="12.375" customWidth="1"/>
-    <col min="12" max="12" width="16.125" customWidth="1"/>
-    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" customWidth="1"/>
+    <col min="6" max="6" width="19.7265625" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="8" max="8" width="36.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.36328125" customWidth="1"/>
+    <col min="10" max="10" width="35.08984375" customWidth="1"/>
+    <col min="11" max="11" width="12.36328125" customWidth="1"/>
+    <col min="12" max="12" width="16.08984375" customWidth="1"/>
+    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.25" thickBot="1">
+    <row r="1" spans="2:21" ht="13.5" thickBot="1">
       <c r="C1" s="91" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="14.25" thickBot="1">
+    <row r="2" spans="2:21" ht="13.5" thickBot="1">
       <c r="B2" s="99" t="s">
         <v>58</v>
       </c>
@@ -25099,7 +26056,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="24"/>
       <c r="C3" s="52" t="s">
         <v>108</v>
@@ -25120,7 +26077,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="14.25" thickTop="1">
+    <row r="4" spans="2:21" ht="13.5" thickTop="1">
       <c r="B4" s="24" t="s">
         <v>221</v>
       </c>
@@ -25134,7 +26091,7 @@
         <v>209</v>
       </c>
       <c r="F4" s="117" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G4" s="116" t="s">
         <v>210</v>
@@ -25152,7 +26109,7 @@
         <v>212</v>
       </c>
       <c r="L4" s="117" t="s">
-        <v>303</v>
+        <v>31</v>
       </c>
       <c r="M4" s="53">
         <f ca="1">LEN(N4)</f>
@@ -25184,7 +26141,7 @@
         <v>209</v>
       </c>
       <c r="F5" s="207" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G5" s="206" t="s">
         <v>210</v>
@@ -25234,7 +26191,7 @@
         <v>209</v>
       </c>
       <c r="F6" s="119" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G6" s="206" t="s">
         <v>210</v>
@@ -25252,7 +26209,7 @@
         <v>212</v>
       </c>
       <c r="L6" s="207" t="s">
-        <v>303</v>
+        <v>31</v>
       </c>
       <c r="M6" s="48">
         <f t="shared" ca="1" si="1"/>
@@ -25290,7 +26247,7 @@
         <v>210</v>
       </c>
       <c r="H7" s="119" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I7" s="206" t="s">
         <v>210</v>
@@ -25302,7 +26259,7 @@
         <v>212</v>
       </c>
       <c r="L7" s="207" t="s">
-        <v>211</v>
+        <v>31</v>
       </c>
       <c r="M7" s="48">
         <f t="shared" ca="1" si="1"/>
@@ -25334,13 +26291,13 @@
         <v>209</v>
       </c>
       <c r="F8" s="207" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G8" s="206" t="s">
         <v>210</v>
       </c>
       <c r="H8" s="208" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I8" s="206" t="s">
         <v>210</v>
@@ -25352,7 +26309,7 @@
         <v>212</v>
       </c>
       <c r="L8" s="207" t="s">
-        <v>303</v>
+        <v>31</v>
       </c>
       <c r="M8" s="48">
         <f t="shared" ca="1" si="1"/>
@@ -25384,13 +26341,13 @@
         <v>209</v>
       </c>
       <c r="F9" s="207" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G9" s="206" t="s">
         <v>210</v>
       </c>
       <c r="H9" s="208" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I9" s="206" t="s">
         <v>210</v>
@@ -25402,7 +26359,7 @@
         <v>212</v>
       </c>
       <c r="L9" s="207" t="s">
-        <v>211</v>
+        <v>31</v>
       </c>
       <c r="M9" s="48">
         <f t="shared" ca="1" si="1"/>
@@ -25434,13 +26391,13 @@
         <v>209</v>
       </c>
       <c r="F10" s="208" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G10" s="206" t="s">
         <v>210</v>
       </c>
       <c r="H10" s="208" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I10" s="206" t="s">
         <v>210</v>
@@ -25452,7 +26409,7 @@
         <v>212</v>
       </c>
       <c r="L10" s="207" t="s">
-        <v>303</v>
+        <v>31</v>
       </c>
       <c r="M10" s="48">
         <f t="shared" ca="1" si="1"/>
@@ -25520,7 +26477,7 @@
       </c>
       <c r="U12" s="29"/>
     </row>
-    <row r="13" spans="2:21" ht="14.25" thickBot="1">
+    <row r="13" spans="2:21" ht="13.5" thickBot="1">
       <c r="B13" s="24"/>
       <c r="C13" s="23"/>
       <c r="D13" s="118"/>
@@ -27771,7 +28728,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="14.25" thickBot="1">
+    <row r="103" spans="2:15" ht="13.5" thickBot="1">
       <c r="B103" s="54"/>
       <c r="C103" s="55"/>
       <c r="D103" s="120"/>
@@ -27844,18 +28801,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.125" customWidth="1"/>
+    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.08984375" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.125" customWidth="1"/>
-    <col min="48" max="48" width="23.625" customWidth="1"/>
+    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.08984375" customWidth="1"/>
+    <col min="48" max="48" width="23.6328125" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -27871,7 +28828,7 @@
       <c r="B2" s="127" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="279" t="s">
+      <c r="C2" s="284" t="s">
         <v>85</v>
       </c>
       <c r="D2" s="59">
@@ -27970,7 +28927,7 @@
       <c r="AI2" s="59">
         <v>0</v>
       </c>
-      <c r="AJ2" s="281" t="s">
+      <c r="AJ2" s="286" t="s">
         <v>51</v>
       </c>
     </row>
@@ -27979,7 +28936,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="280"/>
+      <c r="C3" s="285"/>
       <c r="D3" s="129" t="s">
         <v>61</v>
       </c>
@@ -28061,27 +29018,27 @@
       <c r="AD3" s="130" t="s">
         <v>156</v>
       </c>
-      <c r="AE3" s="283" t="s">
-        <v>305</v>
-      </c>
-      <c r="AF3" s="284"/>
+      <c r="AE3" s="288" t="s">
+        <v>304</v>
+      </c>
+      <c r="AF3" s="289"/>
       <c r="AG3" s="209" t="s">
-        <v>313</v>
-      </c>
-      <c r="AH3" s="283" t="s">
-        <v>312</v>
-      </c>
-      <c r="AI3" s="284"/>
-      <c r="AJ3" s="282"/>
+        <v>311</v>
+      </c>
+      <c r="AH3" s="288" t="s">
+        <v>310</v>
+      </c>
+      <c r="AI3" s="289"/>
+      <c r="AJ3" s="287"/>
       <c r="AR3" s="92" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A4" s="285" t="s">
+    <row r="4" spans="1:49" ht="13.5" thickBot="1">
+      <c r="A4" s="290" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="286"/>
+      <c r="B4" s="291"/>
       <c r="C4" s="192"/>
       <c r="D4" s="192"/>
       <c r="E4" s="192"/>
@@ -28125,9 +29082,9 @@
       <c r="AV4" s="81"/>
       <c r="AW4" s="82"/>
     </row>
-    <row r="5" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A5" s="287"/>
-      <c r="B5" s="288"/>
+    <row r="5" spans="1:49" ht="13.5" thickBot="1">
+      <c r="A5" s="292"/>
+      <c r="B5" s="293"/>
       <c r="C5" s="193"/>
       <c r="D5" s="193"/>
       <c r="E5" s="193"/>
@@ -28574,8 +29531,8 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_O_CHAMAL_PRMRYCHK,                                           /* 02 PRMRYCHK                                        */</v>
       </c>
       <c r="AU8" s="64" t="str">
-        <f ca="1">IF($AW$15&lt;&gt;"NULL","        &amp;"&amp;$AW$15&amp;","&amp;REPT(" ",69-LEN($AW$15))&amp;"/* fp_vd_XDST                                         */","        (void *)NULL,                                                          /* fp_vd_XDST                                         */")</f>
-        <v xml:space="preserve">        &amp;vd_s_AlertO_chamalRwTx,                                               /* fp_vd_XDST                                         */</v>
+        <f ca="1">IF($AW$15&lt;&gt;"NULL","        &amp;"&amp;$AW$15&amp;","&amp;REPT(" ",69-LEN($AW$15))&amp;"/* fp_vd_XDST                                         */","        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */")</f>
+        <v xml:space="preserve">        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */</v>
       </c>
       <c r="AV8" s="50" t="s">
         <v>72</v>
@@ -29507,7 +30464,7 @@
       </c>
       <c r="AW15" s="69" t="str">
         <f ca="1">IF(AW6&lt;&gt;AW17,VLOOKUP(AW6,Matrix!$C$13:$G$37,5,FALSE),Matrix!G13)</f>
-        <v>vd_s_AlertO_chamalRwTx</v>
+        <v>NULL</v>
       </c>
     </row>
     <row r="16" spans="1:49">
@@ -29642,7 +30599,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="14.25" thickBot="1">
+    <row r="17" spans="2:49" ht="13.5" thickBot="1">
       <c r="B17" s="136"/>
       <c r="C17" s="48">
         <f t="shared" si="2"/>
@@ -36054,7 +37011,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="14.25" thickBot="1">
+    <row r="70" spans="1:46" ht="13.5" thickBot="1">
       <c r="A70" s="57" t="s">
         <v>64</v>
       </c>
@@ -56682,39 +57639,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:T134"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="105.875" customWidth="1"/>
-    <col min="3" max="10" width="3.375" customWidth="1"/>
-    <col min="11" max="11" width="20.625" customWidth="1"/>
-    <col min="12" max="12" width="23.375" customWidth="1"/>
-    <col min="13" max="13" width="31.25" customWidth="1"/>
-    <col min="14" max="14" width="20.875" customWidth="1"/>
-    <col min="15" max="15" width="19.375" customWidth="1"/>
-    <col min="16" max="16" width="22.375" customWidth="1"/>
-    <col min="17" max="17" width="15.375" customWidth="1"/>
-    <col min="18" max="18" width="14.125" customWidth="1"/>
+    <col min="2" max="2" width="105.90625" customWidth="1"/>
+    <col min="3" max="10" width="3.36328125" customWidth="1"/>
+    <col min="11" max="11" width="20.6328125" customWidth="1"/>
+    <col min="12" max="12" width="23.36328125" customWidth="1"/>
+    <col min="13" max="13" width="31.26953125" customWidth="1"/>
+    <col min="14" max="14" width="20.90625" customWidth="1"/>
+    <col min="15" max="15" width="19.36328125" customWidth="1"/>
+    <col min="16" max="16" width="22.36328125" customWidth="1"/>
+    <col min="17" max="17" width="15.36328125" customWidth="1"/>
+    <col min="18" max="18" width="14.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="15" thickBot="1">
+    <row r="2" spans="2:18" ht="14.5" thickBot="1">
       <c r="B2" s="25" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="15" thickBot="1">
+    <row r="3" spans="2:18" ht="14.5" thickBot="1">
       <c r="B3" s="96" t="s">
         <v>157</v>
       </c>
-      <c r="C3" s="293" t="s">
+      <c r="C3" s="298" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="294"/>
-      <c r="E3" s="294"/>
-      <c r="F3" s="294"/>
-      <c r="G3" s="294"/>
-      <c r="H3" s="294"/>
-      <c r="I3" s="294"/>
-      <c r="J3" s="295"/>
+      <c r="D3" s="299"/>
+      <c r="E3" s="299"/>
+      <c r="F3" s="299"/>
+      <c r="G3" s="299"/>
+      <c r="H3" s="299"/>
+      <c r="I3" s="299"/>
+      <c r="J3" s="300"/>
       <c r="K3" s="169"/>
       <c r="L3" s="169"/>
       <c r="M3" s="169"/>
@@ -56753,16 +57710,16 @@
       <c r="B5" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="289" t="s">
+      <c r="C5" s="294" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="290"/>
-      <c r="E5" s="290"/>
-      <c r="F5" s="290"/>
-      <c r="G5" s="290"/>
-      <c r="H5" s="290"/>
-      <c r="I5" s="290"/>
-      <c r="J5" s="291"/>
+      <c r="D5" s="295"/>
+      <c r="E5" s="295"/>
+      <c r="F5" s="295"/>
+      <c r="G5" s="295"/>
+      <c r="H5" s="295"/>
+      <c r="I5" s="295"/>
+      <c r="J5" s="296"/>
       <c r="K5" s="35" t="s">
         <v>22</v>
       </c>
@@ -56784,7 +57741,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="27">
+    <row r="6" spans="2:18" ht="26">
       <c r="B6" s="72" t="s">
         <v>33</v>
       </c>
@@ -56831,20 +57788,20 @@
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="27">
+    <row r="7" spans="2:18" ht="26">
       <c r="B7" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="292" t="s">
+      <c r="C7" s="297" t="s">
         <v>163</v>
       </c>
-      <c r="D7" s="290"/>
-      <c r="E7" s="290"/>
-      <c r="F7" s="290"/>
-      <c r="G7" s="290"/>
-      <c r="H7" s="290"/>
-      <c r="I7" s="290"/>
-      <c r="J7" s="291"/>
+      <c r="D7" s="295"/>
+      <c r="E7" s="295"/>
+      <c r="F7" s="295"/>
+      <c r="G7" s="295"/>
+      <c r="H7" s="295"/>
+      <c r="I7" s="295"/>
+      <c r="J7" s="296"/>
       <c r="K7" s="1" t="s">
         <v>218</v>
       </c>
@@ -56862,7 +57819,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="136.5">
+    <row r="8" spans="2:18" ht="131">
       <c r="B8" s="72" t="s">
         <v>28</v>
       </c>
@@ -56891,13 +57848,13 @@
         <v>168</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L8" s="26" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M8" s="26" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="N8" s="29" t="s">
         <v>29</v>
@@ -56962,7 +57919,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="14.25" thickTop="1">
+    <row r="10" spans="2:18" ht="13.5" thickTop="1">
       <c r="B10" s="75" t="s">
         <v>228</v>
       </c>
@@ -58236,7 +59193,7 @@
     </row>
     <row r="34" spans="2:18">
       <c r="B34" s="75" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C34" s="167" t="s">
         <v>169</v>
@@ -58289,7 +59246,7 @@
     </row>
     <row r="35" spans="2:18">
       <c r="B35" s="75" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C35" s="167" t="s">
         <v>169</v>
@@ -58342,7 +59299,7 @@
     </row>
     <row r="36" spans="2:18">
       <c r="B36" s="75" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C36" s="167" t="s">
         <v>169</v>
@@ -58395,7 +59352,7 @@
     </row>
     <row r="37" spans="2:18">
       <c r="B37" s="75" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C37" s="167" t="s">
         <v>169</v>
@@ -58448,7 +59405,7 @@
     </row>
     <row r="38" spans="2:18">
       <c r="B38" s="75" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C38" s="167" t="s">
         <v>169</v>
@@ -58501,7 +59458,7 @@
     </row>
     <row r="39" spans="2:18">
       <c r="B39" s="75" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C39" s="167" t="s">
         <v>169</v>
@@ -58554,7 +59511,7 @@
     </row>
     <row r="40" spans="2:18">
       <c r="B40" s="75" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C40" s="167" t="s">
         <v>169</v>
@@ -58607,7 +59564,7 @@
     </row>
     <row r="41" spans="2:18">
       <c r="B41" s="75" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C41" s="167" t="s">
         <v>169</v>
@@ -58658,7 +59615,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="2:18" ht="14.25" thickBot="1">
+    <row r="42" spans="2:18" ht="13.5" thickBot="1">
       <c r="B42" s="21" t="s">
         <v>273</v>
       </c>
@@ -58713,7 +59670,7 @@
     </row>
     <row r="134" spans="20:20">
       <c r="T134" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -58741,14 +59698,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.25" customWidth="1"/>
+    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="14.25" thickBot="1">
+    <row r="2" spans="2:4" ht="13.5" thickBot="1">
       <c r="B2" s="84" t="s">
         <v>86</v>
       </c>
@@ -58758,7 +59715,7 @@
       </c>
       <c r="D2" s="85"/>
     </row>
-    <row r="3" spans="2:4" ht="14.25" thickBot="1">
+    <row r="3" spans="2:4" ht="13.5" thickBot="1">
       <c r="B3" s="78" t="s">
         <v>86</v>
       </c>
@@ -58769,7 +59726,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="14.25" thickTop="1">
+    <row r="4" spans="2:4" ht="13.5" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -58780,7 +59737,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="40.5">
+    <row r="5" spans="2:4" ht="39">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -58791,7 +59748,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="27">
+    <row r="6" spans="2:4" ht="26">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -58802,7 +59759,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="54">
+    <row r="7" spans="2:4" ht="52">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -58813,7 +59770,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="81">
+    <row r="8" spans="2:4" ht="78">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -58835,7 +59792,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="27">
+    <row r="10" spans="2:4" ht="26">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -58846,7 +59803,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="27">
+    <row r="11" spans="2:4" ht="26">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -58857,7 +59814,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="27">
+    <row r="12" spans="2:4" ht="26">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -58868,7 +59825,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="27">
+    <row r="13" spans="2:4" ht="26">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -58879,7 +59836,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="27">
+    <row r="14" spans="2:4" ht="26">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -58890,7 +59847,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="135">
+    <row r="15" spans="2:4" ht="130">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -58912,7 +59869,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="27">
+    <row r="17" spans="2:4" ht="26">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -58923,7 +59880,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="67.5">
+    <row r="18" spans="2:4" ht="91">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -58934,7 +59891,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="40.5">
+    <row r="19" spans="2:4" ht="39">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -58967,7 +59924,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="27">
+    <row r="22" spans="2:4" ht="26">
       <c r="B22" s="2">
         <v>18</v>
       </c>
@@ -58975,10 +59932,10 @@
         <v>206</v>
       </c>
       <c r="D22" s="90" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="27">
+    <row r="23" spans="2:4" ht="26">
       <c r="B23" s="2">
         <v>19</v>
       </c>
@@ -58986,7 +59943,7 @@
         <v>206</v>
       </c>
       <c r="D23" s="90" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -59004,7 +59961,7 @@
       <c r="C26" s="88"/>
       <c r="D26" s="77"/>
     </row>
-    <row r="27" spans="2:4" ht="14.25" thickBot="1">
+    <row r="27" spans="2:4" ht="13.5" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="89"/>
       <c r="D27" s="5"/>

--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_O_CHAMAL-CSTD-0-00-C-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_O_CHAMAL-CSTD-0-00-C-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\ソフトチーム\20260106_REMWAR_RW\045\IpcApplication\Vom\Alert\matrix\scc\ref更新\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C4C978-E57A-4E30-87BE-E765C99F5B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A36F85A-4F3F-4C1D-8483-6D342D9961C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14535" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="22740" windowHeight="14070" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="13" r:id="rId1"/>
@@ -674,7 +674,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="354">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -3745,6 +3745,25 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>1.1.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RWの削除
+[Reference]シート
+RW記載を対象外に変更</t>
+    <rPh sb="23" eb="25">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>タイショウガイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -5141,7 +5160,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="301">
+  <cellXfs count="305">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5841,18 +5860,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5901,6 +5908,45 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5928,31 +5974,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="68" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -5962,24 +5987,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="50" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -6032,6 +6039,30 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -11198,6 +11229,188 @@
             <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
             <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
           </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5692BBE2-B577-4BAE-92A6-034A08DEB819}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22530955" y="900545"/>
+          <a:ext cx="1073727" cy="9802091"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98AD07D5-EA08-40D7-85B6-85DD1DDC73BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23604682" y="26462183"/>
+          <a:ext cx="17318182" cy="5195454"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -22397,10 +22610,10 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="C1:AM57"/>
-  <sheetFormatPr defaultColWidth="8.08984375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="52" width="2.08984375" style="218" customWidth="1"/>
-    <col min="53" max="16384" width="8.08984375" style="218"/>
+    <col min="1" max="52" width="2.125" style="218" customWidth="1"/>
+    <col min="53" max="16384" width="8.125" style="218"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:20" ht="13.15" customHeight="1"/>
@@ -22463,27 +22676,27 @@
       </c>
     </row>
     <row r="35" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y35" s="239" t="s">
+      <c r="Y35" s="235" t="s">
         <v>331</v>
       </c>
-      <c r="Z35" s="240"/>
-      <c r="AA35" s="240"/>
-      <c r="AB35" s="240"/>
-      <c r="AC35" s="241"/>
-      <c r="AD35" s="239" t="s">
+      <c r="Z35" s="236"/>
+      <c r="AA35" s="236"/>
+      <c r="AB35" s="236"/>
+      <c r="AC35" s="237"/>
+      <c r="AD35" s="235" t="s">
         <v>332</v>
       </c>
-      <c r="AE35" s="240"/>
-      <c r="AF35" s="240"/>
-      <c r="AG35" s="240"/>
-      <c r="AH35" s="241"/>
-      <c r="AI35" s="239" t="s">
+      <c r="AE35" s="236"/>
+      <c r="AF35" s="236"/>
+      <c r="AG35" s="236"/>
+      <c r="AH35" s="237"/>
+      <c r="AI35" s="235" t="s">
         <v>333</v>
       </c>
-      <c r="AJ35" s="240"/>
-      <c r="AK35" s="240"/>
-      <c r="AL35" s="240"/>
-      <c r="AM35" s="241"/>
+      <c r="AJ35" s="236"/>
+      <c r="AK35" s="236"/>
+      <c r="AL35" s="236"/>
+      <c r="AM35" s="237"/>
     </row>
     <row r="36" spans="3:39" ht="13.15" customHeight="1">
       <c r="D36" s="222"/>
@@ -22582,27 +22795,27 @@
       </c>
     </row>
     <row r="43" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y43" s="239" t="s">
+      <c r="Y43" s="235" t="s">
         <v>331</v>
       </c>
-      <c r="Z43" s="240"/>
-      <c r="AA43" s="240"/>
-      <c r="AB43" s="240"/>
-      <c r="AC43" s="241"/>
-      <c r="AD43" s="239" t="s">
+      <c r="Z43" s="236"/>
+      <c r="AA43" s="236"/>
+      <c r="AB43" s="236"/>
+      <c r="AC43" s="237"/>
+      <c r="AD43" s="235" t="s">
         <v>332</v>
       </c>
-      <c r="AE43" s="240"/>
-      <c r="AF43" s="240"/>
-      <c r="AG43" s="240"/>
-      <c r="AH43" s="241"/>
-      <c r="AI43" s="239" t="s">
+      <c r="AE43" s="236"/>
+      <c r="AF43" s="236"/>
+      <c r="AG43" s="236"/>
+      <c r="AH43" s="237"/>
+      <c r="AI43" s="235" t="s">
         <v>333</v>
       </c>
-      <c r="AJ43" s="240"/>
-      <c r="AK43" s="240"/>
-      <c r="AL43" s="240"/>
-      <c r="AM43" s="241"/>
+      <c r="AJ43" s="236"/>
+      <c r="AK43" s="236"/>
+      <c r="AL43" s="236"/>
+      <c r="AM43" s="237"/>
     </row>
     <row r="44" spans="3:39" ht="13.15" customHeight="1">
       <c r="D44" s="222"/>
@@ -22700,27 +22913,27 @@
       </c>
     </row>
     <row r="51" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y51" s="239" t="s">
+      <c r="Y51" s="235" t="s">
         <v>331</v>
       </c>
-      <c r="Z51" s="240"/>
-      <c r="AA51" s="240"/>
-      <c r="AB51" s="240"/>
-      <c r="AC51" s="241"/>
-      <c r="AD51" s="239" t="s">
+      <c r="Z51" s="236"/>
+      <c r="AA51" s="236"/>
+      <c r="AB51" s="236"/>
+      <c r="AC51" s="237"/>
+      <c r="AD51" s="235" t="s">
         <v>332</v>
       </c>
-      <c r="AE51" s="240"/>
-      <c r="AF51" s="240"/>
-      <c r="AG51" s="240"/>
-      <c r="AH51" s="241"/>
-      <c r="AI51" s="239" t="s">
+      <c r="AE51" s="236"/>
+      <c r="AF51" s="236"/>
+      <c r="AG51" s="236"/>
+      <c r="AH51" s="237"/>
+      <c r="AI51" s="235" t="s">
         <v>333</v>
       </c>
-      <c r="AJ51" s="240"/>
-      <c r="AK51" s="240"/>
-      <c r="AL51" s="240"/>
-      <c r="AM51" s="241"/>
+      <c r="AJ51" s="236"/>
+      <c r="AK51" s="236"/>
+      <c r="AL51" s="236"/>
+      <c r="AM51" s="237"/>
     </row>
     <row r="52" spans="4:39" ht="13.15" customHeight="1">
       <c r="D52" s="222"/>
@@ -22837,16 +23050,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="4.36328125" customWidth="1"/>
+    <col min="1" max="1" width="4.375" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.36328125" customWidth="1"/>
-    <col min="5" max="6" width="12.7265625" customWidth="1"/>
-    <col min="7" max="18" width="13.08984375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="69.375" customWidth="1"/>
+    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="18" width="13.125" hidden="1" customWidth="1"/>
     <col min="19" max="22" width="0" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="11" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -22857,18 +23070,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="242" t="s">
+      <c r="I2" s="238" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="M2" s="242"/>
-      <c r="N2" s="242"/>
-      <c r="O2" s="242"/>
-      <c r="P2" s="242"/>
-      <c r="Q2" s="242"/>
-      <c r="R2" s="242"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
+      <c r="M2" s="238"/>
+      <c r="N2" s="238"/>
+      <c r="O2" s="238"/>
+      <c r="P2" s="238"/>
+      <c r="Q2" s="238"/>
+      <c r="R2" s="238"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -22881,25 +23094,25 @@
       <c r="H3" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="I3" s="243" t="s">
+      <c r="I3" s="239" t="s">
         <v>183</v>
       </c>
-      <c r="J3" s="244"/>
-      <c r="K3" s="244"/>
-      <c r="L3" s="244"/>
-      <c r="M3" s="244"/>
-      <c r="N3" s="244"/>
-      <c r="O3" s="244"/>
-      <c r="P3" s="244"/>
-      <c r="Q3" s="244"/>
-      <c r="R3" s="244"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="M3" s="240"/>
+      <c r="N3" s="240"/>
+      <c r="O3" s="240"/>
+      <c r="P3" s="240"/>
+      <c r="Q3" s="240"/>
+      <c r="R3" s="240"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="22" t="str">
         <f>DGET(B8:C14,"Ver.",H4:H5)</f>
-        <v>1.0.2</v>
+        <v>1.1.0</v>
       </c>
       <c r="F4" s="6"/>
       <c r="H4" s="9" t="s">
@@ -22913,45 +23126,45 @@
       <c r="F5" s="6"/>
       <c r="H5" s="11">
         <f>MAX(B9:B14)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:24" ht="13.5" thickBot="1"/>
+    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:24">
-      <c r="C7" s="247" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="248"/>
-      <c r="E7" s="249" t="s">
+      <c r="C7" s="243" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="244"/>
+      <c r="E7" s="245" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="249"/>
-      <c r="G7" s="250" t="s">
+      <c r="F7" s="245"/>
+      <c r="G7" s="246" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="250"/>
-      <c r="I7" s="250"/>
-      <c r="J7" s="250"/>
-      <c r="K7" s="250"/>
-      <c r="L7" s="250"/>
-      <c r="M7" s="251" t="s">
+      <c r="H7" s="246"/>
+      <c r="I7" s="246"/>
+      <c r="J7" s="246"/>
+      <c r="K7" s="246"/>
+      <c r="L7" s="246"/>
+      <c r="M7" s="247" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="251"/>
-      <c r="O7" s="251"/>
-      <c r="P7" s="251"/>
-      <c r="Q7" s="251"/>
-      <c r="R7" s="252"/>
-      <c r="S7" s="245" t="s">
+      <c r="N7" s="247"/>
+      <c r="O7" s="247"/>
+      <c r="P7" s="247"/>
+      <c r="Q7" s="247"/>
+      <c r="R7" s="248"/>
+      <c r="S7" s="241" t="s">
         <v>324</v>
       </c>
-      <c r="T7" s="245"/>
-      <c r="U7" s="245"/>
-      <c r="V7" s="245"/>
-      <c r="W7" s="245"/>
-      <c r="X7" s="246"/>
+      <c r="T7" s="241"/>
+      <c r="U7" s="241"/>
+      <c r="V7" s="241"/>
+      <c r="W7" s="241"/>
+      <c r="X7" s="242"/>
     </row>
-    <row r="8" spans="2:24" ht="26.5" thickBot="1">
+    <row r="8" spans="2:24" ht="27.75" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>15</v>
       </c>
@@ -23022,7 +23235,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="117.5" thickTop="1">
+    <row r="9" spans="2:24" ht="122.25" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -23094,7 +23307,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="39">
+    <row r="10" spans="2:24" ht="40.5">
       <c r="B10" s="9">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
@@ -23166,53 +23379,57 @@
         <v>45811</v>
       </c>
     </row>
-    <row r="11" spans="2:24" ht="117">
+    <row r="11" spans="2:24" ht="121.5">
       <c r="B11" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C11" s="234" t="s">
+      <c r="C11" s="298" t="s">
         <v>348</v>
       </c>
-      <c r="D11" s="235" t="s">
+      <c r="D11" s="299" t="s">
         <v>351</v>
       </c>
-      <c r="E11" s="236" t="s">
+      <c r="E11" s="300" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="236" t="s">
+      <c r="F11" s="300" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="216"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="216"/>
-      <c r="W11" s="237" t="s">
+      <c r="G11" s="301"/>
+      <c r="H11" s="301"/>
+      <c r="I11" s="301"/>
+      <c r="J11" s="301"/>
+      <c r="K11" s="301"/>
+      <c r="L11" s="301"/>
+      <c r="M11" s="301"/>
+      <c r="N11" s="301"/>
+      <c r="O11" s="301"/>
+      <c r="P11" s="301"/>
+      <c r="Q11" s="301"/>
+      <c r="R11" s="301"/>
+      <c r="S11" s="301"/>
+      <c r="T11" s="302"/>
+      <c r="U11" s="301"/>
+      <c r="V11" s="302"/>
+      <c r="W11" s="303" t="s">
         <v>349</v>
       </c>
-      <c r="X11" s="238">
+      <c r="X11" s="304">
         <v>46009</v>
       </c>
     </row>
-    <row r="12" spans="2:24">
+    <row r="12" spans="2:24" ht="40.5">
       <c r="B12" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="C12" s="234" t="s">
+        <v>352</v>
+      </c>
+      <c r="D12" s="297" t="s">
+        <v>353</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -23234,7 +23451,7 @@
       <c r="W12" s="1"/>
       <c r="X12" s="212"/>
     </row>
-    <row r="13" spans="2:24" ht="13.5" thickBot="1">
+    <row r="13" spans="2:24" ht="14.25" thickBot="1">
       <c r="B13" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -23288,11 +23505,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.36328125" customWidth="1"/>
-    <col min="4" max="4" width="17.36328125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.375" customWidth="1"/>
+    <col min="4" max="4" width="17.375" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -23306,13 +23523,13 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1">
+    <row r="6" spans="2:5" ht="14.25" thickBot="1">
       <c r="B6" s="150" t="s">
         <v>128</v>
       </c>
       <c r="C6" s="150"/>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1">
+    <row r="7" spans="2:5" ht="14.25" thickBot="1">
       <c r="C7" s="78" t="s">
         <v>130</v>
       </c>
@@ -23332,7 +23549,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="26">
+    <row r="9" spans="2:5" ht="27">
       <c r="C9" s="160">
         <v>1</v>
       </c>
@@ -23343,7 +23560,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="13.5" thickBot="1">
+    <row r="10" spans="2:5" ht="14.25" thickBot="1">
       <c r="C10" s="158"/>
       <c r="D10" s="89"/>
       <c r="E10" s="5"/>
@@ -23351,14 +23568,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="156"/>
     </row>
-    <row r="12" spans="2:5" ht="13.5" thickBot="1">
+    <row r="12" spans="2:5" ht="14.25" thickBot="1">
       <c r="B12" s="151" t="s">
         <v>129</v>
       </c>
       <c r="C12" s="85"/>
       <c r="D12" s="85"/>
     </row>
-    <row r="13" spans="2:5" ht="13.5" thickBot="1">
+    <row r="13" spans="2:5" ht="14.25" thickBot="1">
       <c r="B13" s="152"/>
       <c r="C13" s="157" t="s">
         <v>130</v>
@@ -23370,7 +23587,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.5" thickTop="1">
+    <row r="14" spans="2:5" ht="14.25" thickTop="1">
       <c r="C14" s="154">
         <v>0</v>
       </c>
@@ -23447,17 +23664,17 @@
         <v>177</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.5" thickBot="1">
+    <row r="21" spans="2:5" ht="14.25" thickBot="1">
       <c r="C21" s="158"/>
       <c r="D21" s="89"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="14.25" thickBot="1">
       <c r="B24" s="150" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.5" thickBot="1">
+    <row r="25" spans="2:5" ht="14.25" thickBot="1">
       <c r="C25" s="157" t="s">
         <v>130</v>
       </c>
@@ -23544,26 +23761,26 @@
       <c r="D33" s="88"/>
       <c r="E33" s="77"/>
     </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1">
+    <row r="34" spans="2:5" ht="14.25" thickBot="1">
       <c r="C34" s="158"/>
       <c r="D34" s="89"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1">
+    <row r="37" spans="2:5" ht="14.25" thickBot="1">
       <c r="B37" s="150" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="253"/>
-      <c r="D38" s="254"/>
+      <c r="C38" s="249"/>
+      <c r="D38" s="250"/>
       <c r="E38" s="114" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.5" thickBot="1">
-      <c r="C39" s="255"/>
-      <c r="D39" s="256"/>
+    <row r="39" spans="2:5" ht="14.25" thickBot="1">
+      <c r="C39" s="251"/>
+      <c r="D39" s="252"/>
       <c r="E39" s="5" t="s">
         <v>119</v>
       </c>
@@ -23592,131 +23809,131 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.7265625" customWidth="1"/>
-    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="269" t="s">
+      <c r="B2" s="275" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="270"/>
-      <c r="D2" s="257" t="s">
+      <c r="C2" s="276"/>
+      <c r="D2" s="266" t="s">
         <v>321</v>
       </c>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259"/>
+      <c r="E2" s="267"/>
+      <c r="F2" s="267"/>
+      <c r="G2" s="267"/>
+      <c r="H2" s="268"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="271" t="s">
+      <c r="B3" s="253" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="272"/>
-      <c r="D3" s="275" t="s">
+      <c r="C3" s="254"/>
+      <c r="D3" s="277" t="s">
         <v>322</v>
       </c>
-      <c r="E3" s="276"/>
-      <c r="F3" s="276"/>
-      <c r="G3" s="276"/>
-      <c r="H3" s="277"/>
+      <c r="E3" s="278"/>
+      <c r="F3" s="278"/>
+      <c r="G3" s="278"/>
+      <c r="H3" s="279"/>
     </row>
-    <row r="4" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B4" s="273" t="s">
+    <row r="4" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B4" s="264" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="274"/>
-      <c r="D4" s="260" t="str">
+      <c r="C4" s="265"/>
+      <c r="D4" s="269" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_O_CHAMAL-CSTD-0-00-C-C0.c</v>
       </c>
-      <c r="E4" s="261"/>
-      <c r="F4" s="261"/>
-      <c r="G4" s="261"/>
-      <c r="H4" s="262"/>
+      <c r="E4" s="270"/>
+      <c r="F4" s="270"/>
+      <c r="G4" s="270"/>
+      <c r="H4" s="271"/>
     </row>
-    <row r="5" spans="2:14" ht="13.5" thickBot="1">
+    <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="269" t="s">
+      <c r="B6" s="275" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="270"/>
-      <c r="D6" s="263" t="str">
+      <c r="C6" s="276"/>
+      <c r="D6" s="272" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>O_CHAMAL</v>
       </c>
-      <c r="E6" s="264"/>
-      <c r="F6" s="264"/>
-      <c r="G6" s="264"/>
-      <c r="H6" s="265"/>
+      <c r="E6" s="273"/>
+      <c r="F6" s="273"/>
+      <c r="G6" s="273"/>
+      <c r="H6" s="274"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="271" t="s">
+      <c r="B7" s="253" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="272"/>
-      <c r="D7" s="266">
+      <c r="C7" s="254"/>
+      <c r="D7" s="255">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="267"/>
-      <c r="F7" s="267"/>
-      <c r="G7" s="267"/>
-      <c r="H7" s="268"/>
+      <c r="E7" s="256"/>
+      <c r="F7" s="256"/>
+      <c r="G7" s="256"/>
+      <c r="H7" s="257"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="271" t="s">
+      <c r="B8" s="253" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="272"/>
-      <c r="D8" s="266" t="str">
+      <c r="C8" s="254"/>
+      <c r="D8" s="255" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_O_CHAMAL_MTRX</v>
       </c>
-      <c r="E8" s="267"/>
-      <c r="F8" s="267"/>
-      <c r="G8" s="267"/>
-      <c r="H8" s="268"/>
+      <c r="E8" s="256"/>
+      <c r="F8" s="256"/>
+      <c r="G8" s="256"/>
+      <c r="H8" s="257"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="271" t="s">
+      <c r="B9" s="253" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="272"/>
-      <c r="D9" s="278" t="s">
+      <c r="C9" s="254"/>
+      <c r="D9" s="258" t="s">
         <v>215</v>
       </c>
-      <c r="E9" s="279"/>
-      <c r="F9" s="279"/>
-      <c r="G9" s="279"/>
-      <c r="H9" s="280"/>
+      <c r="E9" s="259"/>
+      <c r="F9" s="259"/>
+      <c r="G9" s="259"/>
+      <c r="H9" s="260"/>
     </row>
-    <row r="10" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B10" s="273" t="s">
+    <row r="10" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B10" s="264" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="274"/>
-      <c r="D10" s="281"/>
-      <c r="E10" s="282"/>
-      <c r="F10" s="282"/>
-      <c r="G10" s="282"/>
-      <c r="H10" s="283"/>
+      <c r="C10" s="265"/>
+      <c r="D10" s="261"/>
+      <c r="E10" s="262"/>
+      <c r="F10" s="262"/>
+      <c r="G10" s="262"/>
+      <c r="H10" s="263"/>
     </row>
-    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.5" thickBot="1">
+    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="12" spans="2:14" ht="14.25" thickBot="1">
       <c r="B12" s="141" t="s">
         <v>34</v>
       </c>
@@ -23751,7 +23968,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.5" thickTop="1">
+    <row r="13" spans="2:14" ht="14.25" thickTop="1">
       <c r="B13" s="107">
         <v>1</v>
       </c>
@@ -24604,7 +24821,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.5" thickBot="1">
+    <row r="37" spans="2:14" ht="14.25" thickBot="1">
       <c r="B37" s="98">
         <v>25</v>
       </c>
@@ -24645,12 +24862,6 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B8:C8"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="D6:H6"/>
@@ -24661,6 +24872,12 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
@@ -24707,21 +24924,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.36328125" customWidth="1"/>
-    <col min="6" max="6" width="52.7265625" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="44.6328125" customWidth="1"/>
-    <col min="18" max="18" width="73.6328125" customWidth="1"/>
+    <col min="5" max="5" width="36.375" customWidth="1"/>
+    <col min="6" max="6" width="52.75" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.5" thickBot="1">
+    <row r="2" spans="2:18" ht="14.25" thickBot="1">
       <c r="B2" t="s">
         <v>200</v>
       </c>
@@ -24729,7 +24946,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.5" thickBot="1">
+    <row r="3" spans="2:18" ht="14.25" thickBot="1">
       <c r="B3" s="141" t="s">
         <v>34</v>
       </c>
@@ -24767,7 +24984,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B4" s="173">
         <v>0</v>
       </c>
@@ -24795,7 +25012,7 @@
       </c>
       <c r="R4" s="140"/>
     </row>
-    <row r="5" spans="2:18" ht="13.5" thickTop="1">
+    <row r="5" spans="2:18" ht="14.25" thickTop="1">
       <c r="B5" s="176">
         <v>1</v>
       </c>
@@ -25323,7 +25540,7 @@
       <c r="Q28" s="145"/>
       <c r="R28" s="119"/>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="14.25" thickBot="1">
       <c r="B29" s="177">
         <v>25</v>
       </c>
@@ -25345,7 +25562,7 @@
       <c r="Q29" s="143"/>
       <c r="R29" s="121"/>
     </row>
-    <row r="32" spans="2:18" ht="13.5" thickBot="1">
+    <row r="32" spans="2:18" ht="14.25" thickBot="1">
       <c r="B32" t="s">
         <v>201</v>
       </c>
@@ -25353,7 +25570,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.5" thickBot="1">
+    <row r="33" spans="2:18" ht="14.25" thickBot="1">
       <c r="B33" s="141" t="s">
         <v>34</v>
       </c>
@@ -25385,7 +25602,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B34" s="173">
         <v>0</v>
       </c>
@@ -25411,7 +25628,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.5" thickTop="1">
+    <row r="35" spans="2:18" ht="14.25" thickTop="1">
       <c r="B35" s="176">
         <v>1</v>
       </c>
@@ -25939,7 +26156,7 @@
       <c r="Q58" s="145"/>
       <c r="R58" s="178"/>
     </row>
-    <row r="59" spans="2:18" ht="13.5" thickBot="1">
+    <row r="59" spans="2:18" ht="14.25" thickBot="1">
       <c r="B59" s="177">
         <v>25</v>
       </c>
@@ -25990,29 +26207,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.7265625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
-    <col min="8" max="8" width="36.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" customWidth="1"/>
-    <col min="10" max="10" width="35.08984375" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="19.75" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
+    <col min="8" max="8" width="36.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="35.125" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.5" thickBot="1">
+    <row r="1" spans="2:21" ht="14.25" thickBot="1">
       <c r="C1" s="91" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1">
+    <row r="2" spans="2:21" ht="14.25" thickBot="1">
       <c r="B2" s="99" t="s">
         <v>58</v>
       </c>
@@ -26056,7 +26273,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="24"/>
       <c r="C3" s="52" t="s">
         <v>108</v>
@@ -26077,7 +26294,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.5" thickTop="1">
+    <row r="4" spans="2:21" ht="14.25" thickTop="1">
       <c r="B4" s="24" t="s">
         <v>221</v>
       </c>
@@ -26477,7 +26694,7 @@
       </c>
       <c r="U12" s="29"/>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1">
+    <row r="13" spans="2:21" ht="14.25" thickBot="1">
       <c r="B13" s="24"/>
       <c r="C13" s="23"/>
       <c r="D13" s="118"/>
@@ -28728,7 +28945,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.5" thickBot="1">
+    <row r="103" spans="2:15" ht="14.25" thickBot="1">
       <c r="B103" s="54"/>
       <c r="C103" s="55"/>
       <c r="D103" s="120"/>
@@ -28801,18 +29018,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.08984375" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -28828,7 +29045,7 @@
       <c r="B2" s="127" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="284" t="s">
+      <c r="C2" s="280" t="s">
         <v>85</v>
       </c>
       <c r="D2" s="59">
@@ -28927,7 +29144,7 @@
       <c r="AI2" s="59">
         <v>0</v>
       </c>
-      <c r="AJ2" s="286" t="s">
+      <c r="AJ2" s="282" t="s">
         <v>51</v>
       </c>
     </row>
@@ -28936,7 +29153,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="285"/>
+      <c r="C3" s="281"/>
       <c r="D3" s="129" t="s">
         <v>61</v>
       </c>
@@ -29018,27 +29235,27 @@
       <c r="AD3" s="130" t="s">
         <v>156</v>
       </c>
-      <c r="AE3" s="288" t="s">
+      <c r="AE3" s="284" t="s">
         <v>304</v>
       </c>
-      <c r="AF3" s="289"/>
+      <c r="AF3" s="285"/>
       <c r="AG3" s="209" t="s">
         <v>311</v>
       </c>
-      <c r="AH3" s="288" t="s">
+      <c r="AH3" s="284" t="s">
         <v>310</v>
       </c>
-      <c r="AI3" s="289"/>
-      <c r="AJ3" s="287"/>
+      <c r="AI3" s="285"/>
+      <c r="AJ3" s="283"/>
       <c r="AR3" s="92" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A4" s="290" t="s">
+    <row r="4" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A4" s="286" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="291"/>
+      <c r="B4" s="287"/>
       <c r="C4" s="192"/>
       <c r="D4" s="192"/>
       <c r="E4" s="192"/>
@@ -29082,9 +29299,9 @@
       <c r="AV4" s="81"/>
       <c r="AW4" s="82"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A5" s="292"/>
-      <c r="B5" s="293"/>
+    <row r="5" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A5" s="288"/>
+      <c r="B5" s="289"/>
       <c r="C5" s="193"/>
       <c r="D5" s="193"/>
       <c r="E5" s="193"/>
@@ -30599,7 +30816,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="14.25" thickBot="1">
       <c r="B17" s="136"/>
       <c r="C17" s="48">
         <f t="shared" si="2"/>
@@ -37011,7 +37228,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="14.25" thickBot="1">
       <c r="A70" s="57" t="s">
         <v>64</v>
       </c>
@@ -57639,39 +57856,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:T134"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="105.90625" customWidth="1"/>
-    <col min="3" max="10" width="3.36328125" customWidth="1"/>
-    <col min="11" max="11" width="20.6328125" customWidth="1"/>
-    <col min="12" max="12" width="23.36328125" customWidth="1"/>
-    <col min="13" max="13" width="31.26953125" customWidth="1"/>
-    <col min="14" max="14" width="20.90625" customWidth="1"/>
-    <col min="15" max="15" width="19.36328125" customWidth="1"/>
-    <col min="16" max="16" width="22.36328125" customWidth="1"/>
-    <col min="17" max="17" width="15.36328125" customWidth="1"/>
-    <col min="18" max="18" width="14.08984375" customWidth="1"/>
+    <col min="2" max="2" width="105.875" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
+    <col min="11" max="11" width="20.625" customWidth="1"/>
+    <col min="12" max="12" width="23.375" customWidth="1"/>
+    <col min="13" max="13" width="31.25" customWidth="1"/>
+    <col min="14" max="14" width="20.875" customWidth="1"/>
+    <col min="15" max="15" width="19.375" customWidth="1"/>
+    <col min="16" max="16" width="22.375" customWidth="1"/>
+    <col min="17" max="17" width="15.375" customWidth="1"/>
+    <col min="18" max="18" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="14.5" thickBot="1">
+    <row r="2" spans="2:18" ht="15" thickBot="1">
       <c r="B2" s="25" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="14.5" thickBot="1">
+    <row r="3" spans="2:18" ht="15" thickBot="1">
       <c r="B3" s="96" t="s">
         <v>157</v>
       </c>
-      <c r="C3" s="298" t="s">
+      <c r="C3" s="294" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="299"/>
-      <c r="E3" s="299"/>
-      <c r="F3" s="299"/>
-      <c r="G3" s="299"/>
-      <c r="H3" s="299"/>
-      <c r="I3" s="299"/>
-      <c r="J3" s="300"/>
+      <c r="D3" s="295"/>
+      <c r="E3" s="295"/>
+      <c r="F3" s="295"/>
+      <c r="G3" s="295"/>
+      <c r="H3" s="295"/>
+      <c r="I3" s="295"/>
+      <c r="J3" s="296"/>
       <c r="K3" s="169"/>
       <c r="L3" s="169"/>
       <c r="M3" s="169"/>
@@ -57710,16 +57927,16 @@
       <c r="B5" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="294" t="s">
+      <c r="C5" s="290" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="295"/>
-      <c r="E5" s="295"/>
-      <c r="F5" s="295"/>
-      <c r="G5" s="295"/>
-      <c r="H5" s="295"/>
-      <c r="I5" s="295"/>
-      <c r="J5" s="296"/>
+      <c r="D5" s="291"/>
+      <c r="E5" s="291"/>
+      <c r="F5" s="291"/>
+      <c r="G5" s="291"/>
+      <c r="H5" s="291"/>
+      <c r="I5" s="291"/>
+      <c r="J5" s="292"/>
       <c r="K5" s="35" t="s">
         <v>22</v>
       </c>
@@ -57741,7 +57958,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="26">
+    <row r="6" spans="2:18" ht="27">
       <c r="B6" s="72" t="s">
         <v>33</v>
       </c>
@@ -57788,20 +58005,20 @@
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="26">
+    <row r="7" spans="2:18" ht="27">
       <c r="B7" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="297" t="s">
+      <c r="C7" s="293" t="s">
         <v>163</v>
       </c>
-      <c r="D7" s="295"/>
-      <c r="E7" s="295"/>
-      <c r="F7" s="295"/>
-      <c r="G7" s="295"/>
-      <c r="H7" s="295"/>
-      <c r="I7" s="295"/>
-      <c r="J7" s="296"/>
+      <c r="D7" s="291"/>
+      <c r="E7" s="291"/>
+      <c r="F7" s="291"/>
+      <c r="G7" s="291"/>
+      <c r="H7" s="291"/>
+      <c r="I7" s="291"/>
+      <c r="J7" s="292"/>
       <c r="K7" s="1" t="s">
         <v>218</v>
       </c>
@@ -57819,7 +58036,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="131">
+    <row r="8" spans="2:18" ht="136.5">
       <c r="B8" s="72" t="s">
         <v>28</v>
       </c>
@@ -57919,7 +58136,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="13.5" thickTop="1">
+    <row r="10" spans="2:18" ht="14.25" thickTop="1">
       <c r="B10" s="75" t="s">
         <v>228</v>
       </c>
@@ -59615,7 +59832,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="2:18" ht="13.5" thickBot="1">
+    <row r="42" spans="2:18" ht="14.25" thickBot="1">
       <c r="B42" s="21" t="s">
         <v>273</v>
       </c>
@@ -59698,14 +59915,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.5" thickBot="1">
+    <row r="2" spans="2:4" ht="14.25" thickBot="1">
       <c r="B2" s="84" t="s">
         <v>86</v>
       </c>
@@ -59715,7 +59932,7 @@
       </c>
       <c r="D2" s="85"/>
     </row>
-    <row r="3" spans="2:4" ht="13.5" thickBot="1">
+    <row r="3" spans="2:4" ht="14.25" thickBot="1">
       <c r="B3" s="78" t="s">
         <v>86</v>
       </c>
@@ -59726,7 +59943,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.5" thickTop="1">
+    <row r="4" spans="2:4" ht="14.25" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -59737,7 +59954,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39">
+    <row r="5" spans="2:4" ht="40.5">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -59748,7 +59965,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26">
+    <row r="6" spans="2:4" ht="27">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -59759,7 +59976,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52">
+    <row r="7" spans="2:4" ht="54">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -59770,7 +59987,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="78">
+    <row r="8" spans="2:4" ht="81">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -59792,7 +60009,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26">
+    <row r="10" spans="2:4" ht="27">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -59803,7 +60020,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26">
+    <row r="11" spans="2:4" ht="27">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -59814,7 +60031,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26">
+    <row r="12" spans="2:4" ht="27">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -59825,7 +60042,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26">
+    <row r="13" spans="2:4" ht="27">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -59836,7 +60053,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26">
+    <row r="14" spans="2:4" ht="27">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -59847,7 +60064,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="130">
+    <row r="15" spans="2:4" ht="135">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -59869,7 +60086,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26">
+    <row r="17" spans="2:4" ht="27">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -59880,7 +60097,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="91">
+    <row r="18" spans="2:4" ht="67.5">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -59891,7 +60108,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39">
+    <row r="19" spans="2:4" ht="40.5">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -59924,7 +60141,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="26">
+    <row r="22" spans="2:4" ht="27">
       <c r="B22" s="2">
         <v>18</v>
       </c>
@@ -59935,7 +60152,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="26">
+    <row r="23" spans="2:4" ht="27">
       <c r="B23" s="2">
         <v>19</v>
       </c>
@@ -59961,7 +60178,7 @@
       <c r="C26" s="88"/>
       <c r="D26" s="77"/>
     </row>
-    <row r="27" spans="2:4" ht="13.5" thickBot="1">
+    <row r="27" spans="2:4" ht="14.25" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="89"/>
       <c r="D27" s="5"/>
